--- a/research/traditional_assets/database/data/romania/romania_transportation.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_transportation.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1053588479238254</v>
+        <v>0.1052280737671473</v>
       </c>
       <c r="C2">
-        <v>349.0932200768931</v>
+        <v>346.4221316483531</v>
       </c>
       <c r="D2">
-        <v>345.7832200768931</v>
+        <v>346.5441316483531</v>
       </c>
       <c r="E2">
-        <v>-54.8</v>
+        <v>-51.36799999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.432</v>
       </c>
       <c r="G2">
         <v>3.31</v>
@@ -1445,28 +1445,28 @@
         <v>10.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1726296</v>
       </c>
       <c r="N2">
-        <v>10.7</v>
+        <v>10.5273704</v>
       </c>
       <c r="O2">
-        <v>1.712</v>
+        <v>1.684379264</v>
       </c>
       <c r="P2">
-        <v>8.988</v>
+        <v>8.842991135999998</v>
       </c>
       <c r="Q2">
-        <v>21.188</v>
+        <v>21.042991136</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1053588479238254</v>
+        <v>0.1058641957243912</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185858</v>
+        <v>0.8268062626088041</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>61.98241784722897</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1052280737671473</v>
+        <v>0.1050972996104692</v>
       </c>
       <c r="C3">
-        <v>346.4221316483531</v>
+        <v>343.7543994458038</v>
       </c>
       <c r="D3">
-        <v>346.5441316483531</v>
+        <v>347.3083994458038</v>
       </c>
       <c r="E3">
-        <v>-51.36799999999999</v>
+        <v>-47.936</v>
       </c>
       <c r="F3">
-        <v>3.432</v>
+        <v>6.864</v>
       </c>
       <c r="G3">
         <v>3.31</v>
@@ -1527,28 +1527,28 @@
         <v>10.7</v>
       </c>
       <c r="M3">
-        <v>0.1726296</v>
+        <v>0.3452592</v>
       </c>
       <c r="N3">
-        <v>10.5273704</v>
+        <v>10.3547408</v>
       </c>
       <c r="O3">
-        <v>1.684379264</v>
+        <v>1.656758528</v>
       </c>
       <c r="P3">
-        <v>8.842991135999998</v>
+        <v>8.697982272000001</v>
       </c>
       <c r="Q3">
-        <v>21.042991136</v>
+        <v>20.897982272</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1058641957243912</v>
+        <v>0.1063798567453767</v>
       </c>
       <c r="T3">
-        <v>0.8268062626088041</v>
+        <v>0.8339045306600472</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>61.98241784722897</v>
+        <v>30.99120892361449</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1050972996104692</v>
+        <v>0.1049665254537911</v>
       </c>
       <c r="C4">
-        <v>343.7543994458038</v>
+        <v>341.0900457237693</v>
       </c>
       <c r="D4">
-        <v>347.3083994458038</v>
+        <v>348.0760457237693</v>
       </c>
       <c r="E4">
-        <v>-47.936</v>
+        <v>-44.504</v>
       </c>
       <c r="F4">
-        <v>6.864</v>
+        <v>10.296</v>
       </c>
       <c r="G4">
         <v>3.31</v>
@@ -1609,28 +1609,28 @@
         <v>10.7</v>
       </c>
       <c r="M4">
-        <v>0.3452592</v>
+        <v>0.5178887999999999</v>
       </c>
       <c r="N4">
-        <v>10.3547408</v>
+        <v>10.1821112</v>
       </c>
       <c r="O4">
-        <v>1.656758528</v>
+        <v>1.629137792</v>
       </c>
       <c r="P4">
-        <v>8.697982272000001</v>
+        <v>8.552973408</v>
       </c>
       <c r="Q4">
-        <v>20.897982272</v>
+        <v>20.752973408</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1063798567453767</v>
+        <v>0.1069061499523619</v>
       </c>
       <c r="T4">
-        <v>0.8339045306600472</v>
+        <v>0.8411491547535841</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.99120892361449</v>
+        <v>20.66080594907633</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1049665254537911</v>
+        <v>0.1048357512971129</v>
       </c>
       <c r="C5">
-        <v>341.0900457237693</v>
+        <v>338.4290929339639</v>
       </c>
       <c r="D5">
-        <v>348.0760457237693</v>
+        <v>348.8470929339639</v>
       </c>
       <c r="E5">
-        <v>-44.504</v>
+        <v>-41.072</v>
       </c>
       <c r="F5">
-        <v>10.296</v>
+        <v>13.728</v>
       </c>
       <c r="G5">
         <v>3.31</v>
@@ -1691,28 +1691,28 @@
         <v>10.7</v>
       </c>
       <c r="M5">
-        <v>0.5178887999999999</v>
+        <v>0.6905184</v>
       </c>
       <c r="N5">
-        <v>10.1821112</v>
+        <v>10.0094816</v>
       </c>
       <c r="O5">
-        <v>1.629137792</v>
+        <v>1.601517056</v>
       </c>
       <c r="P5">
-        <v>8.552973408</v>
+        <v>8.407964543999999</v>
       </c>
       <c r="Q5">
-        <v>20.752973408</v>
+        <v>20.607964544</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1069061499523619</v>
+        <v>0.1074434076011593</v>
       </c>
       <c r="T5">
-        <v>0.8411491547535841</v>
+        <v>0.8485447085157363</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.66080594907633</v>
+        <v>15.49560446180725</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1048357512971129</v>
+        <v>0.1047679771404348</v>
       </c>
       <c r="C6">
-        <v>338.4290929339639</v>
+        <v>335.3980362710044</v>
       </c>
       <c r="D6">
-        <v>348.8470929339639</v>
+        <v>349.2480362710044</v>
       </c>
       <c r="E6">
-        <v>-41.072</v>
+        <v>-37.64</v>
       </c>
       <c r="F6">
-        <v>13.728</v>
+        <v>17.16</v>
       </c>
       <c r="G6">
         <v>3.31</v>
@@ -1773,45 +1773,45 @@
         <v>10.7</v>
       </c>
       <c r="M6">
-        <v>0.6905184</v>
+        <v>0.888888</v>
       </c>
       <c r="N6">
-        <v>10.0094816</v>
+        <v>9.811112</v>
       </c>
       <c r="O6">
-        <v>1.601517056</v>
+        <v>1.56977792</v>
       </c>
       <c r="P6">
-        <v>8.407964543999999</v>
+        <v>8.24133408</v>
       </c>
       <c r="Q6">
-        <v>20.607964544</v>
+        <v>20.44133408</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1074434076011593</v>
+        <v>0.1079919759372998</v>
       </c>
       <c r="T6">
-        <v>0.8485447085157363</v>
+        <v>0.8560959581465654</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.16</v>
       </c>
       <c r="W6">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.49560446180725</v>
+        <v>12.03751203751204</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1047679771404348</v>
+        <v>0.1046498029837567</v>
       </c>
       <c r="C7">
-        <v>335.3980362710044</v>
+        <v>332.6673485960297</v>
       </c>
       <c r="D7">
-        <v>349.2480362710044</v>
+        <v>349.9493485960297</v>
       </c>
       <c r="E7">
-        <v>-37.64</v>
+        <v>-34.208</v>
       </c>
       <c r="F7">
-        <v>17.16</v>
+        <v>20.592</v>
       </c>
       <c r="G7">
         <v>3.31</v>
@@ -1855,28 +1855,28 @@
         <v>10.7</v>
       </c>
       <c r="M7">
-        <v>0.888888</v>
+        <v>1.0666656</v>
       </c>
       <c r="N7">
-        <v>9.811112</v>
+        <v>9.633334399999999</v>
       </c>
       <c r="O7">
-        <v>1.56977792</v>
+        <v>1.541333504</v>
       </c>
       <c r="P7">
-        <v>8.24133408</v>
+        <v>8.092000895999998</v>
       </c>
       <c r="Q7">
-        <v>20.44133408</v>
+        <v>20.292000896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1079919759372998</v>
+        <v>0.1085522159401667</v>
       </c>
       <c r="T7">
-        <v>0.8560959581465654</v>
+        <v>0.8638078726631568</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.03751203751204</v>
+        <v>10.03126003126003</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1046498029837567</v>
+        <v>0.1046315888270786</v>
       </c>
       <c r="C8">
-        <v>332.6673485960297</v>
+        <v>329.3436923003525</v>
       </c>
       <c r="D8">
-        <v>349.9493485960297</v>
+        <v>350.0576923003525</v>
       </c>
       <c r="E8">
-        <v>-34.208</v>
+        <v>-30.776</v>
       </c>
       <c r="F8">
-        <v>20.592</v>
+        <v>24.024</v>
       </c>
       <c r="G8">
         <v>3.31</v>
@@ -1937,45 +1937,45 @@
         <v>10.7</v>
       </c>
       <c r="M8">
-        <v>1.0666656</v>
+        <v>1.285284</v>
       </c>
       <c r="N8">
-        <v>9.633334399999999</v>
+        <v>9.414715999999999</v>
       </c>
       <c r="O8">
-        <v>1.541333504</v>
+        <v>1.50635456</v>
       </c>
       <c r="P8">
-        <v>8.092000895999998</v>
+        <v>7.908361439999998</v>
       </c>
       <c r="Q8">
-        <v>20.292000896</v>
+        <v>20.10836144</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1085522159401667</v>
+        <v>0.1091245041151383</v>
       </c>
       <c r="T8">
-        <v>0.8638078726631568</v>
+        <v>0.8716856348037609</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.16</v>
       </c>
       <c r="W8">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.03126003126003</v>
+        <v>8.325008325008325</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1046315888270786</v>
+        <v>0.1045814546704005</v>
       </c>
       <c r="C9">
-        <v>329.3436923003526</v>
+        <v>326.2102532544931</v>
       </c>
       <c r="D9">
-        <v>350.0576923003526</v>
+        <v>350.3562532544931</v>
       </c>
       <c r="E9">
-        <v>-30.776</v>
+        <v>-27.344</v>
       </c>
       <c r="F9">
-        <v>24.024</v>
+        <v>27.456</v>
       </c>
       <c r="G9">
         <v>3.31</v>
@@ -2019,45 +2019,45 @@
         <v>10.7</v>
       </c>
       <c r="M9">
-        <v>1.285284</v>
+        <v>1.4908608</v>
       </c>
       <c r="N9">
-        <v>9.414715999999999</v>
+        <v>9.209139199999999</v>
       </c>
       <c r="O9">
-        <v>1.50635456</v>
+        <v>1.473462272</v>
       </c>
       <c r="P9">
-        <v>7.908361439999998</v>
+        <v>7.735676927999999</v>
       </c>
       <c r="Q9">
-        <v>20.10836144</v>
+        <v>19.935676928</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1091245041151383</v>
+        <v>0.1097092333373918</v>
       </c>
       <c r="T9">
-        <v>0.8716856348037609</v>
+        <v>0.8797346526430738</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.16</v>
       </c>
       <c r="W9">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.325008325008323</v>
+        <v>7.177061735072784</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1045814546704005</v>
+        <v>0.1044842805137224</v>
       </c>
       <c r="C10">
-        <v>326.2102532544931</v>
+        <v>323.3584013477965</v>
       </c>
       <c r="D10">
-        <v>350.3562532544931</v>
+        <v>350.9364013477964</v>
       </c>
       <c r="E10">
-        <v>-27.344</v>
+        <v>-23.912</v>
       </c>
       <c r="F10">
-        <v>27.456</v>
+        <v>30.888</v>
       </c>
       <c r="G10">
         <v>3.31</v>
@@ -2101,28 +2101,28 @@
         <v>10.7</v>
       </c>
       <c r="M10">
-        <v>1.4908608</v>
+        <v>1.6772184</v>
       </c>
       <c r="N10">
-        <v>9.209139199999999</v>
+        <v>9.0227816</v>
       </c>
       <c r="O10">
-        <v>1.473462272</v>
+        <v>1.443645056</v>
       </c>
       <c r="P10">
-        <v>7.735676927999999</v>
+        <v>7.579136544</v>
       </c>
       <c r="Q10">
-        <v>19.935676928</v>
+        <v>19.779136544</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1097092333373918</v>
+        <v>0.1103068137513432</v>
       </c>
       <c r="T10">
-        <v>0.8797346526430738</v>
+        <v>0.8879605719733605</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.177061735072784</v>
+        <v>6.379610431175809</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1044842805137224</v>
+        <v>0.1044711063570442</v>
       </c>
       <c r="C11">
-        <v>323.3584013477965</v>
+        <v>320.0052014833739</v>
       </c>
       <c r="D11">
-        <v>350.9364013477964</v>
+        <v>351.0152014833739</v>
       </c>
       <c r="E11">
-        <v>-23.912</v>
+        <v>-20.48</v>
       </c>
       <c r="F11">
-        <v>30.888</v>
+        <v>34.31999999999999</v>
       </c>
       <c r="G11">
         <v>3.31</v>
@@ -2183,45 +2183,45 @@
         <v>10.7</v>
       </c>
       <c r="M11">
-        <v>1.6772184</v>
+        <v>1.897896</v>
       </c>
       <c r="N11">
-        <v>9.0227816</v>
+        <v>8.802104</v>
       </c>
       <c r="O11">
-        <v>1.443645056</v>
+        <v>1.40833664</v>
       </c>
       <c r="P11">
-        <v>7.579136544</v>
+        <v>7.39376736</v>
       </c>
       <c r="Q11">
-        <v>19.779136544</v>
+        <v>19.59376736</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1103068137513432</v>
+        <v>0.1109176737300491</v>
       </c>
       <c r="T11">
-        <v>0.8879605719733605</v>
+        <v>0.896369289510987</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.16</v>
       </c>
       <c r="W11">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.379610431175809</v>
+        <v>5.637822093518297</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1044711063570442</v>
+        <v>0.1043823322003661</v>
       </c>
       <c r="C12">
-        <v>320.0052014833739</v>
+        <v>317.1051208748092</v>
       </c>
       <c r="D12">
-        <v>351.0152014833739</v>
+        <v>351.5471208748093</v>
       </c>
       <c r="E12">
-        <v>-20.48</v>
+        <v>-17.04799999999999</v>
       </c>
       <c r="F12">
-        <v>34.32</v>
+        <v>37.752</v>
       </c>
       <c r="G12">
         <v>3.31</v>
@@ -2265,28 +2265,28 @@
         <v>10.7</v>
       </c>
       <c r="M12">
-        <v>1.897896</v>
+        <v>2.0876856</v>
       </c>
       <c r="N12">
-        <v>8.802104</v>
+        <v>8.612314399999999</v>
       </c>
       <c r="O12">
-        <v>1.40833664</v>
+        <v>1.377970304</v>
       </c>
       <c r="P12">
-        <v>7.39376736</v>
+        <v>7.234344095999999</v>
       </c>
       <c r="Q12">
-        <v>19.59376736</v>
+        <v>19.434344096</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1109176737300491</v>
+        <v>0.1115422608992878</v>
       </c>
       <c r="T12">
-        <v>0.896369289510987</v>
+        <v>0.9049669669932794</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.637822093518296</v>
+        <v>5.125292812289358</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1043823322003661</v>
+        <v>0.104293558043688</v>
       </c>
       <c r="C13">
-        <v>317.1051208748092</v>
+        <v>314.2066548267871</v>
       </c>
       <c r="D13">
-        <v>351.5471208748093</v>
+        <v>352.0806548267871</v>
       </c>
       <c r="E13">
-        <v>-17.04799999999999</v>
+        <v>-13.616</v>
       </c>
       <c r="F13">
-        <v>37.752</v>
+        <v>41.184</v>
       </c>
       <c r="G13">
         <v>3.31</v>
@@ -2347,28 +2347,28 @@
         <v>10.7</v>
       </c>
       <c r="M13">
-        <v>2.0876856</v>
+        <v>2.2774752</v>
       </c>
       <c r="N13">
-        <v>8.612314399999999</v>
+        <v>8.4225248</v>
       </c>
       <c r="O13">
-        <v>1.377970304</v>
+        <v>1.347603968</v>
       </c>
       <c r="P13">
-        <v>7.234344095999999</v>
+        <v>7.074920832</v>
       </c>
       <c r="Q13">
-        <v>19.434344096</v>
+        <v>19.274920832</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1115422608992878</v>
+        <v>0.1121810432314636</v>
       </c>
       <c r="T13">
-        <v>0.9049669669932794</v>
+        <v>0.9137600462365328</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.125292812289358</v>
+        <v>4.698185077931913</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.104293558043688</v>
+        <v>0.1044777838870099</v>
       </c>
       <c r="C14">
-        <v>314.2066548267871</v>
+        <v>309.6692559644563</v>
       </c>
       <c r="D14">
-        <v>352.0806548267871</v>
+        <v>350.9752559644563</v>
       </c>
       <c r="E14">
-        <v>-13.616</v>
+        <v>-10.184</v>
       </c>
       <c r="F14">
-        <v>41.184</v>
+        <v>44.616</v>
       </c>
       <c r="G14">
         <v>3.31</v>
@@ -2429,45 +2429,45 @@
         <v>10.7</v>
       </c>
       <c r="M14">
-        <v>2.2774752</v>
+        <v>2.5788048</v>
       </c>
       <c r="N14">
-        <v>8.4225248</v>
+        <v>8.121195199999999</v>
       </c>
       <c r="O14">
-        <v>1.347603968</v>
+        <v>1.299391232</v>
       </c>
       <c r="P14">
-        <v>7.074920832</v>
+        <v>6.821803967999999</v>
       </c>
       <c r="Q14">
-        <v>19.274920832</v>
+        <v>19.021803968</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1121810432314636</v>
+        <v>0.1128345102149539</v>
       </c>
       <c r="T14">
-        <v>0.9137600462365328</v>
+        <v>0.9227552652325048</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.16</v>
       </c>
       <c r="W14">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.698185077931913</v>
+        <v>4.149208966882641</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1044777838870099</v>
+        <v>0.1048216097303317</v>
       </c>
       <c r="C15">
-        <v>309.6692559644563</v>
+        <v>304.1926766329462</v>
       </c>
       <c r="D15">
-        <v>350.9752559644563</v>
+        <v>348.9306766329462</v>
       </c>
       <c r="E15">
-        <v>-10.184</v>
+        <v>-6.751999999999995</v>
       </c>
       <c r="F15">
-        <v>44.616</v>
+        <v>48.048</v>
       </c>
       <c r="G15">
         <v>3.31</v>
@@ -2511,45 +2511,45 @@
         <v>10.7</v>
       </c>
       <c r="M15">
-        <v>2.5788048</v>
+        <v>2.9453424</v>
       </c>
       <c r="N15">
-        <v>8.121195199999999</v>
+        <v>7.7546576</v>
       </c>
       <c r="O15">
-        <v>1.299391232</v>
+        <v>1.240745216</v>
       </c>
       <c r="P15">
-        <v>6.821803967999999</v>
+        <v>6.513912383999999</v>
       </c>
       <c r="Q15">
-        <v>19.021803968</v>
+        <v>18.713912384</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1128345102149539</v>
+        <v>0.1135031741050369</v>
       </c>
       <c r="T15">
-        <v>0.9227552652325048</v>
+        <v>0.931959675367918</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.16</v>
       </c>
       <c r="W15">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.149208966882641</v>
+        <v>3.632854366948984</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1048216097303317</v>
+        <v>0.1051360355736536</v>
       </c>
       <c r="C16">
-        <v>304.1926766329462</v>
+        <v>298.9116683330068</v>
       </c>
       <c r="D16">
-        <v>348.9306766329462</v>
+        <v>347.0816683330068</v>
       </c>
       <c r="E16">
-        <v>-6.751999999999995</v>
+        <v>-3.319999999999993</v>
       </c>
       <c r="F16">
-        <v>48.048</v>
+        <v>51.48</v>
       </c>
       <c r="G16">
         <v>3.31</v>
@@ -2593,45 +2593,45 @@
         <v>10.7</v>
       </c>
       <c r="M16">
-        <v>2.9453424</v>
+        <v>3.299868</v>
       </c>
       <c r="N16">
-        <v>7.7546576</v>
+        <v>7.400131999999999</v>
       </c>
       <c r="O16">
-        <v>1.240745216</v>
+        <v>1.18402112</v>
       </c>
       <c r="P16">
-        <v>6.513912383999999</v>
+        <v>6.21611088</v>
       </c>
       <c r="Q16">
-        <v>18.713912384</v>
+        <v>18.41611088</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1135031741050369</v>
+        <v>0.1141875712631219</v>
       </c>
       <c r="T16">
-        <v>0.931959675367918</v>
+        <v>0.9413806598594585</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.16</v>
       </c>
       <c r="W16">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.632854366948984</v>
+        <v>3.242553944582025</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1051360355736536</v>
+        <v>0.1051211814169755</v>
       </c>
       <c r="C17">
-        <v>298.9116683330068</v>
+        <v>295.5665783600558</v>
       </c>
       <c r="D17">
-        <v>347.0816683330068</v>
+        <v>347.1685783600557</v>
       </c>
       <c r="E17">
-        <v>-3.32</v>
+        <v>0.1120000000000019</v>
       </c>
       <c r="F17">
-        <v>51.48</v>
+        <v>54.912</v>
       </c>
       <c r="G17">
         <v>3.31</v>
@@ -2675,28 +2675,28 @@
         <v>10.7</v>
       </c>
       <c r="M17">
-        <v>3.299868</v>
+        <v>3.5198592</v>
       </c>
       <c r="N17">
-        <v>7.400131999999999</v>
+        <v>7.180140799999999</v>
       </c>
       <c r="O17">
-        <v>1.18402112</v>
+        <v>1.148822528</v>
       </c>
       <c r="P17">
-        <v>6.21611088</v>
+        <v>6.031318271999999</v>
       </c>
       <c r="Q17">
-        <v>18.41611088</v>
+        <v>18.231318272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1141875712631219</v>
+        <v>0.1148882635916375</v>
       </c>
       <c r="T17">
-        <v>0.9413806598594585</v>
+        <v>0.9510259535055594</v>
       </c>
       <c r="U17">
         <v>0.0641</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.242553944582026</v>
+        <v>3.039894323045649</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1051211814169755</v>
+        <v>0.1062201672602974</v>
       </c>
       <c r="C18">
-        <v>295.5665783600558</v>
+        <v>285.8199094313817</v>
       </c>
       <c r="D18">
-        <v>347.1685783600557</v>
+        <v>340.8539094313817</v>
       </c>
       <c r="E18">
-        <v>0.1120000000000019</v>
+        <v>3.544000000000004</v>
       </c>
       <c r="F18">
-        <v>54.912</v>
+        <v>58.344</v>
       </c>
       <c r="G18">
         <v>3.31</v>
@@ -2757,45 +2757,45 @@
         <v>10.7</v>
       </c>
       <c r="M18">
-        <v>3.5198592</v>
+        <v>4.194933600000001</v>
       </c>
       <c r="N18">
-        <v>7.180140799999999</v>
+        <v>6.505066399999999</v>
       </c>
       <c r="O18">
-        <v>1.148822528</v>
+        <v>1.040810624</v>
       </c>
       <c r="P18">
-        <v>6.031318271999999</v>
+        <v>5.464255775999999</v>
       </c>
       <c r="Q18">
-        <v>18.231318272</v>
+        <v>17.664255776</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1148882635916375</v>
+        <v>0.1156058400726475</v>
       </c>
       <c r="T18">
-        <v>0.9510259535055594</v>
+        <v>0.9609036638660244</v>
       </c>
       <c r="U18">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V18">
         <v>0.16</v>
       </c>
       <c r="W18">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.039894323045649</v>
+        <v>2.550695915663599</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1062201672602974</v>
+        <v>0.1068605131036193</v>
       </c>
       <c r="C19">
-        <v>285.8199094313817</v>
+        <v>278.8133508010931</v>
       </c>
       <c r="D19">
-        <v>340.8539094313817</v>
+        <v>337.2793508010931</v>
       </c>
       <c r="E19">
-        <v>3.544000000000004</v>
+        <v>6.976000000000006</v>
       </c>
       <c r="F19">
-        <v>58.344</v>
+        <v>61.776</v>
       </c>
       <c r="G19">
         <v>3.31</v>
@@ -2839,45 +2839,45 @@
         <v>10.7</v>
       </c>
       <c r="M19">
-        <v>4.194933600000001</v>
+        <v>4.6826208</v>
       </c>
       <c r="N19">
-        <v>6.505066399999999</v>
+        <v>6.017379199999999</v>
       </c>
       <c r="O19">
-        <v>1.040810624</v>
+        <v>0.9627806719999998</v>
       </c>
       <c r="P19">
-        <v>5.464255775999999</v>
+        <v>5.054598527999999</v>
       </c>
       <c r="Q19">
-        <v>17.664255776</v>
+        <v>17.254598528</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1156058400726475</v>
+        <v>0.1163409184190479</v>
       </c>
       <c r="T19">
-        <v>0.9609036638660244</v>
+        <v>0.9710222939913786</v>
       </c>
       <c r="U19">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.16</v>
       </c>
       <c r="W19">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.550695915663599</v>
+        <v>2.285045161034606</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1068605131036193</v>
+        <v>0.1069439389469411</v>
       </c>
       <c r="C20">
-        <v>278.813350801093</v>
+        <v>274.9211610462254</v>
       </c>
       <c r="D20">
-        <v>337.279350801093</v>
+        <v>336.8191610462254</v>
       </c>
       <c r="E20">
-        <v>6.975999999999999</v>
+        <v>10.408</v>
       </c>
       <c r="F20">
-        <v>61.776</v>
+        <v>65.208</v>
       </c>
       <c r="G20">
         <v>3.31</v>
@@ -2921,28 +2921,28 @@
         <v>10.7</v>
       </c>
       <c r="M20">
-        <v>4.6826208</v>
+        <v>4.9427664</v>
       </c>
       <c r="N20">
-        <v>6.017379199999999</v>
+        <v>5.757233599999999</v>
       </c>
       <c r="O20">
-        <v>0.9627806719999998</v>
+        <v>0.9211573759999999</v>
       </c>
       <c r="P20">
-        <v>5.054598527999999</v>
+        <v>4.836076223999999</v>
       </c>
       <c r="Q20">
-        <v>17.254598528</v>
+        <v>17.036076224</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1163409184190479</v>
+        <v>0.1170941468480755</v>
       </c>
       <c r="T20">
-        <v>0.9710222939913786</v>
+        <v>0.9813907668358773</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.285045161034606</v>
+        <v>2.164779626243312</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1069439389469411</v>
+        <v>0.107027364790263</v>
       </c>
       <c r="C21">
-        <v>274.9211610462254</v>
+        <v>271.0302253619361</v>
       </c>
       <c r="D21">
-        <v>336.8191610462254</v>
+        <v>336.360225361936</v>
       </c>
       <c r="E21">
-        <v>10.408</v>
+        <v>13.84</v>
       </c>
       <c r="F21">
-        <v>65.208</v>
+        <v>68.64</v>
       </c>
       <c r="G21">
         <v>3.31</v>
@@ -3003,28 +3003,28 @@
         <v>10.7</v>
       </c>
       <c r="M21">
-        <v>4.9427664</v>
+        <v>5.202912</v>
       </c>
       <c r="N21">
-        <v>5.757233599999999</v>
+        <v>5.497087999999999</v>
       </c>
       <c r="O21">
-        <v>0.9211573759999999</v>
+        <v>0.8795340799999999</v>
       </c>
       <c r="P21">
-        <v>4.836076223999999</v>
+        <v>4.617553919999999</v>
       </c>
       <c r="Q21">
-        <v>17.036076224</v>
+        <v>16.81755392</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1170941468480755</v>
+        <v>0.1178662059878288</v>
       </c>
       <c r="T21">
-        <v>0.9813907668358773</v>
+        <v>0.9920184515014888</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.164779626243312</v>
+        <v>2.056540644931146</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.107027364790263</v>
+        <v>0.1096156706335849</v>
       </c>
       <c r="C22">
-        <v>271.0302253619361</v>
+        <v>253.9557590504219</v>
       </c>
       <c r="D22">
-        <v>336.360225361936</v>
+        <v>322.7177590504219</v>
       </c>
       <c r="E22">
-        <v>13.84</v>
+        <v>17.27200000000001</v>
       </c>
       <c r="F22">
-        <v>68.64</v>
+        <v>72.072</v>
       </c>
       <c r="G22">
         <v>3.31</v>
@@ -3085,45 +3085,45 @@
         <v>10.7</v>
       </c>
       <c r="M22">
-        <v>5.202912</v>
+        <v>6.48648</v>
       </c>
       <c r="N22">
-        <v>5.497087999999999</v>
+        <v>4.213519999999999</v>
       </c>
       <c r="O22">
-        <v>0.8795340799999999</v>
+        <v>0.6741631999999999</v>
       </c>
       <c r="P22">
-        <v>4.617553919999999</v>
+        <v>3.539356799999999</v>
       </c>
       <c r="Q22">
-        <v>16.81755392</v>
+        <v>15.7393568</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1178662059878288</v>
+        <v>0.1186578109285885</v>
       </c>
       <c r="T22">
-        <v>0.9920184515014888</v>
+        <v>1.00291519147509</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.16</v>
       </c>
       <c r="W22">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.056540644931146</v>
+        <v>1.649584982918316</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1096156706335849</v>
+        <v>0.1098183764769068</v>
       </c>
       <c r="C23">
-        <v>253.9557590504219</v>
+        <v>249.5019153376739</v>
       </c>
       <c r="D23">
-        <v>322.7177590504219</v>
+        <v>321.695915337674</v>
       </c>
       <c r="E23">
-        <v>17.27199999999999</v>
+        <v>20.70400000000001</v>
       </c>
       <c r="F23">
-        <v>72.07199999999999</v>
+        <v>75.504</v>
       </c>
       <c r="G23">
         <v>3.31</v>
@@ -3167,28 +3167,28 @@
         <v>10.7</v>
       </c>
       <c r="M23">
-        <v>6.486479999999998</v>
+        <v>6.795360000000001</v>
       </c>
       <c r="N23">
-        <v>4.213520000000001</v>
+        <v>3.904639999999999</v>
       </c>
       <c r="O23">
-        <v>0.6741632000000002</v>
+        <v>0.6247423999999998</v>
       </c>
       <c r="P23">
-        <v>3.539356800000001</v>
+        <v>3.279897599999999</v>
       </c>
       <c r="Q23">
-        <v>15.7393568</v>
+        <v>15.4798976</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1186578109285885</v>
+        <v>0.1194697134319317</v>
       </c>
       <c r="T23">
-        <v>1.00291519147509</v>
+        <v>1.014091335037758</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.649584982918316</v>
+        <v>1.57460384733112</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1098183764769068</v>
+        <v>0.1100210823202286</v>
       </c>
       <c r="C24">
-        <v>249.5019153376739</v>
+        <v>245.0545222696068</v>
       </c>
       <c r="D24">
-        <v>321.695915337674</v>
+        <v>320.6805222696069</v>
       </c>
       <c r="E24">
-        <v>20.70400000000001</v>
+        <v>24.13600000000001</v>
       </c>
       <c r="F24">
-        <v>75.504</v>
+        <v>78.93600000000001</v>
       </c>
       <c r="G24">
         <v>3.31</v>
@@ -3249,28 +3249,28 @@
         <v>10.7</v>
       </c>
       <c r="M24">
-        <v>6.795360000000001</v>
+        <v>7.104240000000001</v>
       </c>
       <c r="N24">
-        <v>3.904639999999999</v>
+        <v>3.595759999999999</v>
       </c>
       <c r="O24">
-        <v>0.6247423999999998</v>
+        <v>0.5753215999999998</v>
       </c>
       <c r="P24">
-        <v>3.279897599999999</v>
+        <v>3.020438399999999</v>
       </c>
       <c r="Q24">
-        <v>15.4798976</v>
+        <v>15.2204384</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1194697134319317</v>
+        <v>0.1203027043119853</v>
       </c>
       <c r="T24">
-        <v>1.014091335037758</v>
+        <v>1.025557768043613</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.57460384733112</v>
+        <v>1.506142810490636</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1100210823202286</v>
+        <v>0.1225866604249054</v>
       </c>
       <c r="C25">
-        <v>245.0545222696068</v>
+        <v>189.1454887988256</v>
       </c>
       <c r="D25">
-        <v>320.6805222696069</v>
+        <v>268.2034887988256</v>
       </c>
       <c r="E25">
-        <v>24.13600000000001</v>
+        <v>27.56800000000001</v>
       </c>
       <c r="F25">
-        <v>78.93600000000001</v>
+        <v>82.36800000000001</v>
       </c>
       <c r="G25">
         <v>3.31</v>
@@ -3331,45 +3331,45 @@
         <v>10.7</v>
       </c>
       <c r="M25">
-        <v>7.104240000000001</v>
+        <v>12.0916224</v>
       </c>
       <c r="N25">
-        <v>3.595759999999999</v>
+        <v>-1.391622400000003</v>
       </c>
       <c r="O25">
-        <v>0.5753215999999998</v>
+        <v>-0.2226595840000005</v>
       </c>
       <c r="P25">
-        <v>3.020438399999999</v>
+        <v>-1.168962816000002</v>
       </c>
       <c r="Q25">
-        <v>15.2204384</v>
+        <v>11.031037184</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1203027043119853</v>
+        <v>0.1215039544911189</v>
       </c>
       <c r="T25">
-        <v>1.025557768043613</v>
+        <v>1.042093428915941</v>
       </c>
       <c r="U25">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.16</v>
+        <v>0.1415856320488473</v>
       </c>
       <c r="W25">
-        <v>0.0756</v>
+        <v>0.1260152292152292</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y25">
-        <v>1.506142810490636</v>
+        <v>0.8849102003052954</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1225866604249054</v>
+        <v>0.1235966604249054</v>
       </c>
       <c r="C26">
-        <v>189.1454887988256</v>
+        <v>182.2315202643497</v>
       </c>
       <c r="D26">
-        <v>268.2034887988256</v>
+        <v>264.7215202643497</v>
       </c>
       <c r="E26">
-        <v>27.568</v>
+        <v>31</v>
       </c>
       <c r="F26">
-        <v>82.36799999999999</v>
+        <v>85.8</v>
       </c>
       <c r="G26">
         <v>3.31</v>
@@ -3413,37 +3413,37 @@
         <v>10.7</v>
       </c>
       <c r="M26">
-        <v>12.0916224</v>
+        <v>12.59544</v>
       </c>
       <c r="N26">
-        <v>-1.391622400000001</v>
+        <v>-1.895440000000001</v>
       </c>
       <c r="O26">
-        <v>-0.2226595840000002</v>
+        <v>-0.3032704000000001</v>
       </c>
       <c r="P26">
-        <v>-1.168962816000001</v>
+        <v>-1.592169600000001</v>
       </c>
       <c r="Q26">
-        <v>11.031037184</v>
+        <v>10.6078304</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1215039544911189</v>
+        <v>0.1225133405510005</v>
       </c>
       <c r="T26">
-        <v>1.042093428915941</v>
+        <v>1.055988007968153</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.1415856320488473</v>
+        <v>0.1359222067668934</v>
       </c>
       <c r="W26">
-        <v>0.1260152292152292</v>
+        <v>0.1268466200466201</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8849102003052955</v>
+        <v>0.8495137922930838</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1235966604249054</v>
+        <v>0.1246066604249054</v>
       </c>
       <c r="C27">
-        <v>182.2315202643497</v>
+        <v>175.4068027703537</v>
       </c>
       <c r="D27">
-        <v>264.7215202643497</v>
+        <v>261.3288027703537</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>34.432</v>
       </c>
       <c r="F27">
-        <v>85.8</v>
+        <v>89.232</v>
       </c>
       <c r="G27">
         <v>3.31</v>
@@ -3495,37 +3495,37 @@
         <v>10.7</v>
       </c>
       <c r="M27">
-        <v>12.59544</v>
+        <v>13.0992576</v>
       </c>
       <c r="N27">
-        <v>-1.895440000000001</v>
+        <v>-2.399257600000002</v>
       </c>
       <c r="O27">
-        <v>-0.3032704000000001</v>
+        <v>-0.3838812160000004</v>
       </c>
       <c r="P27">
-        <v>-1.592169600000001</v>
+        <v>-2.015376384000002</v>
       </c>
       <c r="Q27">
-        <v>10.6078304</v>
+        <v>10.184623616</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1225133405510005</v>
+        <v>0.1235500073152032</v>
       </c>
       <c r="T27">
-        <v>1.055988007968153</v>
+        <v>1.070258116183939</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1359222067668934</v>
+        <v>0.1306944295835513</v>
       </c>
       <c r="W27">
-        <v>0.1268466200466201</v>
+        <v>0.1276140577371347</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8495137922930838</v>
+        <v>0.8168401848971959</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1246066604249054</v>
+        <v>0.1407409208610162</v>
       </c>
       <c r="C28">
-        <v>175.4068027703537</v>
+        <v>127.5645850779613</v>
       </c>
       <c r="D28">
-        <v>261.3288027703537</v>
+        <v>216.9185850779613</v>
       </c>
       <c r="E28">
-        <v>34.432</v>
+        <v>37.864</v>
       </c>
       <c r="F28">
-        <v>89.232</v>
+        <v>92.664</v>
       </c>
       <c r="G28">
         <v>3.31</v>
@@ -3577,45 +3577,45 @@
         <v>10.7</v>
       </c>
       <c r="M28">
-        <v>13.0992576</v>
+        <v>18.6069312</v>
       </c>
       <c r="N28">
-        <v>-2.399257600000002</v>
+        <v>-7.906931200000002</v>
       </c>
       <c r="O28">
-        <v>-0.3838812160000004</v>
+        <v>-1.265108992</v>
       </c>
       <c r="P28">
-        <v>-2.015376384000002</v>
+        <v>-6.641822208000002</v>
       </c>
       <c r="Q28">
-        <v>10.184623616</v>
+        <v>5.558177791999997</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1235500073152032</v>
+        <v>0.1253606381498099</v>
       </c>
       <c r="T28">
-        <v>1.070258116183939</v>
+        <v>1.095182131152768</v>
       </c>
       <c r="U28">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1306944295835513</v>
+        <v>0.09200872414683835</v>
       </c>
       <c r="W28">
-        <v>0.1276140577371347</v>
+        <v>0.1823246481913149</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.8168401848971959</v>
+        <v>0.5750545259177396</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1407409208610162</v>
+        <v>0.1422909208610162</v>
       </c>
       <c r="C29">
-        <v>127.5645850779613</v>
+        <v>120.64807271275</v>
       </c>
       <c r="D29">
-        <v>216.9185850779613</v>
+        <v>213.43407271275</v>
       </c>
       <c r="E29">
-        <v>37.864</v>
+        <v>41.29600000000001</v>
       </c>
       <c r="F29">
-        <v>92.664</v>
+        <v>96.096</v>
       </c>
       <c r="G29">
         <v>3.31</v>
@@ -3659,37 +3659,37 @@
         <v>10.7</v>
       </c>
       <c r="M29">
-        <v>18.6069312</v>
+        <v>19.2960768</v>
       </c>
       <c r="N29">
-        <v>-7.906931200000002</v>
+        <v>-8.596076800000002</v>
       </c>
       <c r="O29">
-        <v>-1.265108992</v>
+        <v>-1.375372288</v>
       </c>
       <c r="P29">
-        <v>-6.641822208000002</v>
+        <v>-7.220704512000002</v>
       </c>
       <c r="Q29">
-        <v>5.558177791999997</v>
+        <v>4.979295487999997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1253606381498099</v>
+        <v>0.1264656470130017</v>
       </c>
       <c r="T29">
-        <v>1.095182131152768</v>
+        <v>1.110392994085445</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.09200872414683835</v>
+        <v>0.08872269828445126</v>
       </c>
       <c r="W29">
-        <v>0.1823246481913149</v>
+        <v>0.1829844821844822</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5750545259177396</v>
+        <v>0.5545168642778204</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1422909208610162</v>
+        <v>0.1438409208610162</v>
       </c>
       <c r="C30">
-        <v>120.64807271275</v>
+        <v>113.8417387122182</v>
       </c>
       <c r="D30">
-        <v>213.43407271275</v>
+        <v>210.0597387122182</v>
       </c>
       <c r="E30">
-        <v>41.29600000000001</v>
+        <v>44.72800000000001</v>
       </c>
       <c r="F30">
-        <v>96.096</v>
+        <v>99.52800000000001</v>
       </c>
       <c r="G30">
         <v>3.31</v>
@@ -3741,37 +3741,37 @@
         <v>10.7</v>
       </c>
       <c r="M30">
-        <v>19.2960768</v>
+        <v>19.9852224</v>
       </c>
       <c r="N30">
-        <v>-8.596076800000002</v>
+        <v>-9.285222400000002</v>
       </c>
       <c r="O30">
-        <v>-1.375372288</v>
+        <v>-1.485635584</v>
       </c>
       <c r="P30">
-        <v>-7.220704512000002</v>
+        <v>-7.799586816000001</v>
       </c>
       <c r="Q30">
-        <v>4.979295487999997</v>
+        <v>4.400413183999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1264656470130017</v>
+        <v>0.1276017828864243</v>
       </c>
       <c r="T30">
-        <v>1.110392994085445</v>
+        <v>1.126032332030311</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.08872269828445126</v>
+        <v>0.08566329489533224</v>
       </c>
       <c r="W30">
-        <v>0.1829844821844822</v>
+        <v>0.1835988103850173</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5545168642778204</v>
+        <v>0.5353955930958265</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1438409208610162</v>
+        <v>0.1453909208610162</v>
       </c>
       <c r="C31">
-        <v>113.8417387122183</v>
+        <v>107.1404387379936</v>
       </c>
       <c r="D31">
-        <v>210.0597387122183</v>
+        <v>206.7904387379936</v>
       </c>
       <c r="E31">
-        <v>44.72799999999999</v>
+        <v>48.16</v>
       </c>
       <c r="F31">
-        <v>99.52799999999999</v>
+        <v>102.96</v>
       </c>
       <c r="G31">
         <v>3.31</v>
@@ -3823,37 +3823,37 @@
         <v>10.7</v>
       </c>
       <c r="M31">
-        <v>19.9852224</v>
+        <v>20.674368</v>
       </c>
       <c r="N31">
-        <v>-9.285222399999999</v>
+        <v>-9.974367999999998</v>
       </c>
       <c r="O31">
-        <v>-1.485635584</v>
+        <v>-1.59589888</v>
       </c>
       <c r="P31">
-        <v>-7.799586815999999</v>
+        <v>-8.378469119999998</v>
       </c>
       <c r="Q31">
-        <v>4.400413184</v>
+        <v>3.821530880000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1276017828864242</v>
+        <v>0.1287703797848017</v>
       </c>
       <c r="T31">
-        <v>1.126032332030311</v>
+        <v>1.142118508202172</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.08566329489533227</v>
+        <v>0.08280785173215453</v>
       </c>
       <c r="W31">
-        <v>0.1835988103850173</v>
+        <v>0.1841721833721834</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5353955930958267</v>
+        <v>0.5175490733259658</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1453909208610162</v>
+        <v>0.1469409208610162</v>
       </c>
       <c r="C32">
-        <v>107.1404387379936</v>
+        <v>100.5393438027759</v>
       </c>
       <c r="D32">
-        <v>206.7904387379936</v>
+        <v>203.6213438027759</v>
       </c>
       <c r="E32">
-        <v>48.16</v>
+        <v>51.592</v>
       </c>
       <c r="F32">
-        <v>102.96</v>
+        <v>106.392</v>
       </c>
       <c r="G32">
         <v>3.31</v>
@@ -3905,37 +3905,37 @@
         <v>10.7</v>
       </c>
       <c r="M32">
-        <v>20.674368</v>
+        <v>21.3635136</v>
       </c>
       <c r="N32">
-        <v>-9.974367999999998</v>
+        <v>-10.6635136</v>
       </c>
       <c r="O32">
-        <v>-1.59589888</v>
+        <v>-1.706162176</v>
       </c>
       <c r="P32">
-        <v>-8.378469119999998</v>
+        <v>-8.957351424000002</v>
       </c>
       <c r="Q32">
-        <v>3.821530880000001</v>
+        <v>3.242648575999997</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1287703797848017</v>
+        <v>0.1299728490570453</v>
       </c>
       <c r="T32">
-        <v>1.142118508202172</v>
+        <v>1.15867095035003</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.08280785173215453</v>
+        <v>0.08013663070853662</v>
       </c>
       <c r="W32">
-        <v>0.1841721833721834</v>
+        <v>0.1847085645537259</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5175490733259658</v>
+        <v>0.500853941928354</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1469409208610162</v>
+        <v>0.159910536520924</v>
       </c>
       <c r="C33">
-        <v>100.5393438027759</v>
+        <v>73.96407719661381</v>
       </c>
       <c r="D33">
-        <v>203.6213438027759</v>
+        <v>180.4780771966138</v>
       </c>
       <c r="E33">
-        <v>51.592</v>
+        <v>55.024</v>
       </c>
       <c r="F33">
-        <v>106.392</v>
+        <v>109.824</v>
       </c>
       <c r="G33">
         <v>3.31</v>
@@ -3987,45 +3987,45 @@
         <v>10.7</v>
       </c>
       <c r="M33">
-        <v>21.3635136</v>
+        <v>25.8964992</v>
       </c>
       <c r="N33">
-        <v>-10.6635136</v>
+        <v>-15.1964992</v>
       </c>
       <c r="O33">
-        <v>-1.706162176</v>
+        <v>-2.431439872</v>
       </c>
       <c r="P33">
-        <v>-8.957351424000002</v>
+        <v>-12.765059328</v>
       </c>
       <c r="Q33">
-        <v>3.242648575999997</v>
+        <v>-0.565059328000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1299728490570453</v>
+        <v>0.1315336492783367</v>
       </c>
       <c r="T33">
-        <v>1.15867095035003</v>
+        <v>1.180155952889087</v>
       </c>
       <c r="U33">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08013663070853662</v>
+        <v>0.06610932183451267</v>
       </c>
       <c r="W33">
-        <v>0.1847085645537259</v>
+        <v>0.2202114219114219</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.500853941928354</v>
+        <v>0.4131832614657042</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.159910536520924</v>
+        <v>0.161810536520924</v>
       </c>
       <c r="C34">
-        <v>73.96407719661381</v>
+        <v>67.57623924467296</v>
       </c>
       <c r="D34">
-        <v>180.4780771966138</v>
+        <v>177.522239244673</v>
       </c>
       <c r="E34">
-        <v>55.024</v>
+        <v>58.456</v>
       </c>
       <c r="F34">
-        <v>109.824</v>
+        <v>113.256</v>
       </c>
       <c r="G34">
         <v>3.31</v>
@@ -4069,37 +4069,37 @@
         <v>10.7</v>
       </c>
       <c r="M34">
-        <v>25.8964992</v>
+        <v>26.7057648</v>
       </c>
       <c r="N34">
-        <v>-15.1964992</v>
+        <v>-16.0057648</v>
       </c>
       <c r="O34">
-        <v>-2.431439872</v>
+        <v>-2.560922368</v>
       </c>
       <c r="P34">
-        <v>-12.765059328</v>
+        <v>-13.444842432</v>
       </c>
       <c r="Q34">
-        <v>-0.565059328000002</v>
+        <v>-1.244842432000002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1315336492783367</v>
+        <v>0.1328132559839835</v>
       </c>
       <c r="T34">
-        <v>1.180155952889087</v>
+        <v>1.197770220842656</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06610932183451267</v>
+        <v>0.06410600905164865</v>
       </c>
       <c r="W34">
-        <v>0.2202114219114219</v>
+        <v>0.2206838030656213</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.4131832614657042</v>
+        <v>0.400662556572804</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.161810536520924</v>
+        <v>0.163710536520924</v>
       </c>
       <c r="C35">
-        <v>67.57623924467296</v>
+        <v>61.28366151754996</v>
       </c>
       <c r="D35">
-        <v>177.522239244673</v>
+        <v>174.66166151755</v>
       </c>
       <c r="E35">
-        <v>58.456</v>
+        <v>61.88800000000001</v>
       </c>
       <c r="F35">
-        <v>113.256</v>
+        <v>116.688</v>
       </c>
       <c r="G35">
         <v>3.31</v>
@@ -4151,37 +4151,37 @@
         <v>10.7</v>
       </c>
       <c r="M35">
-        <v>26.7057648</v>
+        <v>27.5150304</v>
       </c>
       <c r="N35">
-        <v>-16.0057648</v>
+        <v>-16.8150304</v>
       </c>
       <c r="O35">
-        <v>-2.560922368</v>
+        <v>-2.690404864</v>
       </c>
       <c r="P35">
-        <v>-13.444842432</v>
+        <v>-14.124625536</v>
       </c>
       <c r="Q35">
-        <v>-1.244842432000002</v>
+        <v>-1.924625536000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1328132559839835</v>
+        <v>0.1341316386504075</v>
       </c>
       <c r="T35">
-        <v>1.197770220842656</v>
+        <v>1.215918254491787</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06410600905164865</v>
+        <v>0.0622205381971884</v>
       </c>
       <c r="W35">
-        <v>0.2206838030656213</v>
+        <v>0.221128397093103</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.400662556572804</v>
+        <v>0.3888783637324275</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.163710536520924</v>
+        <v>0.165610536520924</v>
       </c>
       <c r="C36">
-        <v>61.28366151754996</v>
+        <v>55.08181199913648</v>
       </c>
       <c r="D36">
-        <v>174.66166151755</v>
+        <v>171.8918119991365</v>
       </c>
       <c r="E36">
-        <v>61.88800000000001</v>
+        <v>65.32000000000001</v>
       </c>
       <c r="F36">
-        <v>116.688</v>
+        <v>120.12</v>
       </c>
       <c r="G36">
         <v>3.31</v>
@@ -4233,37 +4233,37 @@
         <v>10.7</v>
       </c>
       <c r="M36">
-        <v>27.5150304</v>
+        <v>28.324296</v>
       </c>
       <c r="N36">
-        <v>-16.8150304</v>
+        <v>-17.624296</v>
       </c>
       <c r="O36">
-        <v>-2.690404864</v>
+        <v>-2.819887360000001</v>
       </c>
       <c r="P36">
-        <v>-14.124625536</v>
+        <v>-14.80440864</v>
       </c>
       <c r="Q36">
-        <v>-1.924625536000001</v>
+        <v>-2.604408640000004</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1341316386504075</v>
+        <v>0.1354905869373369</v>
       </c>
       <c r="T36">
-        <v>1.215918254491787</v>
+        <v>1.234624689176276</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0622205381971884</v>
+        <v>0.06044280853441158</v>
       </c>
       <c r="W36">
-        <v>0.221128397093103</v>
+        <v>0.2215475857475858</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3888783637324275</v>
+        <v>0.3777675533400724</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.165610536520924</v>
+        <v>0.167510536520924</v>
       </c>
       <c r="C37">
-        <v>55.08181199913648</v>
+        <v>48.96644166708465</v>
       </c>
       <c r="D37">
-        <v>171.8918119991365</v>
+        <v>169.2084416670847</v>
       </c>
       <c r="E37">
-        <v>65.32000000000001</v>
+        <v>68.75200000000001</v>
       </c>
       <c r="F37">
-        <v>120.12</v>
+        <v>123.552</v>
       </c>
       <c r="G37">
         <v>3.31</v>
@@ -4315,37 +4315,37 @@
         <v>10.7</v>
       </c>
       <c r="M37">
-        <v>28.324296</v>
+        <v>29.1335616</v>
       </c>
       <c r="N37">
-        <v>-17.624296</v>
+        <v>-18.4335616</v>
       </c>
       <c r="O37">
-        <v>-2.819887360000001</v>
+        <v>-2.949369856000001</v>
       </c>
       <c r="P37">
-        <v>-14.80440864</v>
+        <v>-15.484191744</v>
       </c>
       <c r="Q37">
-        <v>-2.604408640000004</v>
+        <v>-3.284191744000005</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1354905869373369</v>
+        <v>0.1368920023582328</v>
       </c>
       <c r="T37">
-        <v>1.234624689176276</v>
+        <v>1.253915699944655</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.06044280853441158</v>
+        <v>0.05876384163067792</v>
       </c>
       <c r="W37">
-        <v>0.2215475857475858</v>
+        <v>0.2219434861434862</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3777675533400724</v>
+        <v>0.367274010191737</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.167510536520924</v>
+        <v>0.169410536520924</v>
       </c>
       <c r="C38">
-        <v>48.96644166708464</v>
+        <v>42.93356274352264</v>
       </c>
       <c r="D38">
-        <v>169.2084416670846</v>
+        <v>166.6075627435226</v>
       </c>
       <c r="E38">
-        <v>68.752</v>
+        <v>72.184</v>
       </c>
       <c r="F38">
-        <v>123.552</v>
+        <v>126.984</v>
       </c>
       <c r="G38">
         <v>3.31</v>
@@ -4397,37 +4397,37 @@
         <v>10.7</v>
       </c>
       <c r="M38">
-        <v>29.1335616</v>
+        <v>29.9428272</v>
       </c>
       <c r="N38">
-        <v>-18.4335616</v>
+        <v>-19.2428272</v>
       </c>
       <c r="O38">
-        <v>-2.949369856</v>
+        <v>-3.078852352</v>
       </c>
       <c r="P38">
-        <v>-15.484191744</v>
+        <v>-16.163974848</v>
       </c>
       <c r="Q38">
-        <v>-3.284191744000001</v>
+        <v>-3.963974848000003</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1368920023582328</v>
+        <v>0.1383379071575698</v>
       </c>
       <c r="T38">
-        <v>1.253915699944655</v>
+        <v>1.273819123753301</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05876384163067793</v>
+        <v>0.05717562969471367</v>
       </c>
       <c r="W38">
-        <v>0.2219434861434862</v>
+        <v>0.2223179865179865</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.367274010191737</v>
+        <v>0.3573476855919604</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.169410536520924</v>
+        <v>0.171310536520924</v>
       </c>
       <c r="C39">
-        <v>42.93356274352264</v>
+        <v>36.97942892123655</v>
       </c>
       <c r="D39">
-        <v>166.6075627435226</v>
+        <v>164.0854289212365</v>
       </c>
       <c r="E39">
-        <v>72.184</v>
+        <v>75.616</v>
       </c>
       <c r="F39">
-        <v>126.984</v>
+        <v>130.416</v>
       </c>
       <c r="G39">
         <v>3.31</v>
@@ -4479,37 +4479,37 @@
         <v>10.7</v>
       </c>
       <c r="M39">
-        <v>29.9428272</v>
+        <v>30.7520928</v>
       </c>
       <c r="N39">
-        <v>-19.2428272</v>
+        <v>-20.0520928</v>
       </c>
       <c r="O39">
-        <v>-3.078852352</v>
+        <v>-3.208334848</v>
       </c>
       <c r="P39">
-        <v>-16.163974848</v>
+        <v>-16.843757952</v>
       </c>
       <c r="Q39">
-        <v>-3.963974848000003</v>
+        <v>-4.643757952000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1383379071575698</v>
+        <v>0.139830454047208</v>
       </c>
       <c r="T39">
-        <v>1.273819123753301</v>
+        <v>1.294364593491257</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05717562969471367</v>
+        <v>0.05567100786064225</v>
       </c>
       <c r="W39">
-        <v>0.2223179865179865</v>
+        <v>0.2226727763464606</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3573476855919604</v>
+        <v>0.3479437991290141</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.171310536520924</v>
+        <v>0.173210536520924</v>
       </c>
       <c r="C40">
-        <v>36.97942892123655</v>
+        <v>31.10051735910562</v>
       </c>
       <c r="D40">
-        <v>164.0854289212365</v>
+        <v>161.6385173591056</v>
       </c>
       <c r="E40">
-        <v>75.616</v>
+        <v>79.04800000000002</v>
       </c>
       <c r="F40">
-        <v>130.416</v>
+        <v>133.848</v>
       </c>
       <c r="G40">
         <v>3.31</v>
@@ -4561,37 +4561,37 @@
         <v>10.7</v>
       </c>
       <c r="M40">
-        <v>30.7520928</v>
+        <v>31.5613584</v>
       </c>
       <c r="N40">
-        <v>-20.0520928</v>
+        <v>-20.8613584</v>
       </c>
       <c r="O40">
-        <v>-3.208334848</v>
+        <v>-3.337817344000001</v>
       </c>
       <c r="P40">
-        <v>-16.843757952</v>
+        <v>-17.523541056</v>
       </c>
       <c r="Q40">
-        <v>-4.643757952000001</v>
+        <v>-5.323541056000003</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.139830454047208</v>
+        <v>0.1413719369004409</v>
       </c>
       <c r="T40">
-        <v>1.294364593491257</v>
+        <v>1.315583685187835</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05567100786064225</v>
+        <v>0.05424354612062578</v>
       </c>
       <c r="W40">
-        <v>0.2226727763464606</v>
+        <v>0.2230093718247564</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3479437991290141</v>
+        <v>0.3390221632539111</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.173210536520924</v>
+        <v>0.175110536520924</v>
       </c>
       <c r="C41">
-        <v>31.10051735910562</v>
+        <v>25.29351226481771</v>
       </c>
       <c r="D41">
-        <v>161.6385173591056</v>
+        <v>159.2635122648177</v>
       </c>
       <c r="E41">
-        <v>79.04800000000002</v>
+        <v>82.48</v>
       </c>
       <c r="F41">
-        <v>133.848</v>
+        <v>137.28</v>
       </c>
       <c r="G41">
         <v>3.31</v>
@@ -4643,37 +4643,37 @@
         <v>10.7</v>
       </c>
       <c r="M41">
-        <v>31.5613584</v>
+        <v>32.370624</v>
       </c>
       <c r="N41">
-        <v>-20.8613584</v>
+        <v>-21.670624</v>
       </c>
       <c r="O41">
-        <v>-3.337817344000001</v>
+        <v>-3.46729984</v>
       </c>
       <c r="P41">
-        <v>-17.523541056</v>
+        <v>-18.20332416</v>
       </c>
       <c r="Q41">
-        <v>-5.323541056000003</v>
+        <v>-6.003324160000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1413719369004409</v>
+        <v>0.1429648025154483</v>
       </c>
       <c r="T41">
-        <v>1.315583685187835</v>
+        <v>1.337510079940966</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05424354612062578</v>
+        <v>0.05288745746761014</v>
       </c>
       <c r="W41">
-        <v>0.2230093718247564</v>
+        <v>0.2233291375291376</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3390221632539111</v>
+        <v>0.3305466091725634</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.175110536520924</v>
+        <v>0.177010536520924</v>
       </c>
       <c r="C42">
-        <v>25.29351226481771</v>
+        <v>19.55528990397173</v>
       </c>
       <c r="D42">
-        <v>159.2635122648177</v>
+        <v>156.9572899039717</v>
       </c>
       <c r="E42">
-        <v>82.48</v>
+        <v>85.91200000000002</v>
       </c>
       <c r="F42">
-        <v>137.28</v>
+        <v>140.712</v>
       </c>
       <c r="G42">
         <v>3.31</v>
@@ -4725,37 +4725,37 @@
         <v>10.7</v>
       </c>
       <c r="M42">
-        <v>32.370624</v>
+        <v>33.1798896</v>
       </c>
       <c r="N42">
-        <v>-21.670624</v>
+        <v>-22.4798896</v>
       </c>
       <c r="O42">
-        <v>-3.46729984</v>
+        <v>-3.596782336</v>
       </c>
       <c r="P42">
-        <v>-18.20332416</v>
+        <v>-18.883107264</v>
       </c>
       <c r="Q42">
-        <v>-6.003324160000002</v>
+        <v>-6.683107264000004</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1429648025154483</v>
+        <v>0.1446116635750321</v>
       </c>
       <c r="T42">
-        <v>1.337510079940966</v>
+        <v>1.360179742312846</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05288745746761014</v>
+        <v>0.05159751948059525</v>
       </c>
       <c r="W42">
-        <v>0.2233291375291376</v>
+        <v>0.2236333049064756</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3305466091725634</v>
+        <v>0.3224844967537203</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.177010536520924</v>
+        <v>0.178910536520924</v>
       </c>
       <c r="C43">
-        <v>19.55528990397173</v>
+        <v>13.88290489304762</v>
       </c>
       <c r="D43">
-        <v>156.9572899039717</v>
+        <v>154.7169048930476</v>
       </c>
       <c r="E43">
-        <v>85.91200000000002</v>
+        <v>89.34400000000001</v>
       </c>
       <c r="F43">
-        <v>140.712</v>
+        <v>144.144</v>
       </c>
       <c r="G43">
         <v>3.31</v>
@@ -4807,37 +4807,37 @@
         <v>10.7</v>
       </c>
       <c r="M43">
-        <v>33.1798896</v>
+        <v>33.98915520000001</v>
       </c>
       <c r="N43">
-        <v>-22.4798896</v>
+        <v>-23.28915520000001</v>
       </c>
       <c r="O43">
-        <v>-3.596782336</v>
+        <v>-3.726264832000001</v>
       </c>
       <c r="P43">
-        <v>-18.883107264</v>
+        <v>-19.56289036800001</v>
       </c>
       <c r="Q43">
-        <v>-6.683107264000004</v>
+        <v>-7.362890368000006</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1446116635750321</v>
+        <v>0.1463153129470154</v>
       </c>
       <c r="T43">
-        <v>1.360179742312846</v>
+        <v>1.383631117180309</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05159751948059525</v>
+        <v>0.05036900711200964</v>
       </c>
       <c r="W43">
-        <v>0.2236333049064756</v>
+        <v>0.2239229881229881</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3224844967537203</v>
+        <v>0.3148062944500603</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.178910536520924</v>
+        <v>0.180810536520924</v>
       </c>
       <c r="C44">
-        <v>13.88290489304765</v>
+        <v>8.273577649768129</v>
       </c>
       <c r="D44">
-        <v>154.7169048930476</v>
+        <v>152.5395776497681</v>
       </c>
       <c r="E44">
-        <v>89.34399999999998</v>
+        <v>92.776</v>
       </c>
       <c r="F44">
-        <v>144.144</v>
+        <v>147.576</v>
       </c>
       <c r="G44">
         <v>3.31</v>
@@ -4889,37 +4889,37 @@
         <v>10.7</v>
       </c>
       <c r="M44">
-        <v>33.9891552</v>
+        <v>34.7984208</v>
       </c>
       <c r="N44">
-        <v>-23.2891552</v>
+        <v>-24.0984208</v>
       </c>
       <c r="O44">
-        <v>-3.726264832</v>
+        <v>-3.855747328000001</v>
       </c>
       <c r="P44">
-        <v>-19.562890368</v>
+        <v>-20.242673472</v>
       </c>
       <c r="Q44">
-        <v>-7.362890367999999</v>
+        <v>-8.042673472000004</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1463153129470154</v>
+        <v>0.1480787394899455</v>
       </c>
       <c r="T44">
-        <v>1.383631117180309</v>
+        <v>1.407905347306279</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05036900711200966</v>
+        <v>0.04919763485359083</v>
       </c>
       <c r="W44">
-        <v>0.2239229881229881</v>
+        <v>0.2241991977015233</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3148062944500604</v>
+        <v>0.3074852178349426</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.180810536520924</v>
+        <v>0.182710536520924</v>
       </c>
       <c r="C45">
-        <v>8.273577649768129</v>
+        <v>2.724682888419551</v>
       </c>
       <c r="D45">
-        <v>152.5395776497681</v>
+        <v>150.4226828884196</v>
       </c>
       <c r="E45">
-        <v>92.776</v>
+        <v>96.20800000000001</v>
       </c>
       <c r="F45">
-        <v>147.576</v>
+        <v>151.008</v>
       </c>
       <c r="G45">
         <v>3.31</v>
@@ -4971,37 +4971,37 @@
         <v>10.7</v>
       </c>
       <c r="M45">
-        <v>34.7984208</v>
+        <v>35.60768640000001</v>
       </c>
       <c r="N45">
-        <v>-24.0984208</v>
+        <v>-24.90768640000001</v>
       </c>
       <c r="O45">
-        <v>-3.855747328000001</v>
+        <v>-3.985229824000001</v>
       </c>
       <c r="P45">
-        <v>-20.242673472</v>
+        <v>-20.92245657600001</v>
       </c>
       <c r="Q45">
-        <v>-8.042673472000004</v>
+        <v>-8.722456576000006</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1480787394899455</v>
+        <v>0.149905145552266</v>
       </c>
       <c r="T45">
-        <v>1.407905347306279</v>
+        <v>1.433046514222463</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04919763485359083</v>
+        <v>0.04807950678873648</v>
       </c>
       <c r="W45">
-        <v>0.2241991977015233</v>
+        <v>0.2244628522992159</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3074852178349426</v>
+        <v>0.300496917429603</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.182710536520924</v>
+        <v>0.184610536520924</v>
       </c>
       <c r="C46">
-        <v>2.724682888419551</v>
+        <v>-2.766260939990104</v>
       </c>
       <c r="D46">
-        <v>150.4226828884196</v>
+        <v>148.3637390600099</v>
       </c>
       <c r="E46">
-        <v>96.20800000000001</v>
+        <v>99.64</v>
       </c>
       <c r="F46">
-        <v>151.008</v>
+        <v>154.44</v>
       </c>
       <c r="G46">
         <v>3.31</v>
@@ -5053,37 +5053,37 @@
         <v>10.7</v>
       </c>
       <c r="M46">
-        <v>35.60768640000001</v>
+        <v>36.416952</v>
       </c>
       <c r="N46">
-        <v>-24.90768640000001</v>
+        <v>-25.716952</v>
       </c>
       <c r="O46">
-        <v>-3.985229824000001</v>
+        <v>-4.114712320000001</v>
       </c>
       <c r="P46">
-        <v>-20.92245657600001</v>
+        <v>-21.60223968</v>
       </c>
       <c r="Q46">
-        <v>-8.722456576000006</v>
+        <v>-9.402239680000005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.149905145552266</v>
+        <v>0.151797966380489</v>
       </c>
       <c r="T46">
-        <v>1.433046514222463</v>
+        <v>1.459101905390144</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04807950678873648</v>
+        <v>0.04701107330454234</v>
       </c>
       <c r="W46">
-        <v>0.2244628522992159</v>
+        <v>0.2247147889147889</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.300496917429603</v>
+        <v>0.2938192081533896</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.184610536520924</v>
+        <v>0.186510536520924</v>
       </c>
       <c r="C47">
-        <v>-2.766260939990104</v>
+        <v>-8.201601352043099</v>
       </c>
       <c r="D47">
-        <v>148.3637390600099</v>
+        <v>146.3603986479569</v>
       </c>
       <c r="E47">
-        <v>99.64</v>
+        <v>103.072</v>
       </c>
       <c r="F47">
-        <v>154.44</v>
+        <v>157.872</v>
       </c>
       <c r="G47">
         <v>3.31</v>
@@ -5135,37 +5135,37 @@
         <v>10.7</v>
       </c>
       <c r="M47">
-        <v>36.416952</v>
+        <v>37.22621760000001</v>
       </c>
       <c r="N47">
-        <v>-25.716952</v>
+        <v>-26.52621760000001</v>
       </c>
       <c r="O47">
-        <v>-4.114712320000001</v>
+        <v>-4.244194816000001</v>
       </c>
       <c r="P47">
-        <v>-21.60223968</v>
+        <v>-22.28202278400001</v>
       </c>
       <c r="Q47">
-        <v>-9.402239680000005</v>
+        <v>-10.08202278400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.151797966380489</v>
+        <v>0.1537608916838314</v>
       </c>
       <c r="T47">
-        <v>1.459101905390144</v>
+        <v>1.486122311045517</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04701107330454234</v>
+        <v>0.04598909345009577</v>
       </c>
       <c r="W47">
-        <v>0.2247147889147889</v>
+        <v>0.2249557717644674</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2938192081533896</v>
+        <v>0.2874318340630985</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.186510536520924</v>
+        <v>0.188410536520924</v>
       </c>
       <c r="C48">
-        <v>-8.201601352043099</v>
+        <v>-13.58356076047934</v>
       </c>
       <c r="D48">
-        <v>146.3603986479569</v>
+        <v>144.4104392395207</v>
       </c>
       <c r="E48">
-        <v>103.072</v>
+        <v>106.504</v>
       </c>
       <c r="F48">
-        <v>157.872</v>
+        <v>161.304</v>
       </c>
       <c r="G48">
         <v>3.31</v>
@@ -5217,37 +5217,37 @@
         <v>10.7</v>
       </c>
       <c r="M48">
-        <v>37.22621760000001</v>
+        <v>38.0354832</v>
       </c>
       <c r="N48">
-        <v>-26.52621760000001</v>
+        <v>-27.3354832</v>
       </c>
       <c r="O48">
-        <v>-4.244194816000001</v>
+        <v>-4.373677312000001</v>
       </c>
       <c r="P48">
-        <v>-22.28202278400001</v>
+        <v>-22.961805888</v>
       </c>
       <c r="Q48">
-        <v>-10.08202278400001</v>
+        <v>-10.761805888</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1537608916838314</v>
+        <v>0.1557978896401301</v>
       </c>
       <c r="T48">
-        <v>1.486122311045517</v>
+        <v>1.51416235465015</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04598909345009577</v>
+        <v>0.04501060210009374</v>
       </c>
       <c r="W48">
-        <v>0.2249557717644674</v>
+        <v>0.2251865000247979</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2874318340630985</v>
+        <v>0.2813162631255858</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.188410536520924</v>
+        <v>0.190310536520924</v>
       </c>
       <c r="C49">
-        <v>-13.58356076047934</v>
+        <v>-18.91424469841741</v>
       </c>
       <c r="D49">
-        <v>144.4104392395207</v>
+        <v>142.5117553015826</v>
       </c>
       <c r="E49">
-        <v>106.504</v>
+        <v>109.936</v>
       </c>
       <c r="F49">
-        <v>161.304</v>
+        <v>164.736</v>
       </c>
       <c r="G49">
         <v>3.31</v>
@@ -5299,37 +5299,37 @@
         <v>10.7</v>
       </c>
       <c r="M49">
-        <v>38.0354832</v>
+        <v>38.8447488</v>
       </c>
       <c r="N49">
-        <v>-27.3354832</v>
+        <v>-28.14474880000001</v>
       </c>
       <c r="O49">
-        <v>-4.373677312000001</v>
+        <v>-4.503159808000001</v>
       </c>
       <c r="P49">
-        <v>-22.961805888</v>
+        <v>-23.641588992</v>
       </c>
       <c r="Q49">
-        <v>-10.761805888</v>
+        <v>-11.441588992</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1557978896401301</v>
+        <v>0.1579132336716711</v>
       </c>
       <c r="T49">
-        <v>1.51416235465015</v>
+        <v>1.543280861470345</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04501060210009374</v>
+        <v>0.04407288122300845</v>
       </c>
       <c r="W49">
-        <v>0.2251865000247979</v>
+        <v>0.2254076146076146</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2813162631255858</v>
+        <v>0.2754555076438028</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.190310536520924</v>
+        <v>0.192210536520924</v>
       </c>
       <c r="C50">
-        <v>-18.91424469841738</v>
+        <v>-24.19564940320993</v>
       </c>
       <c r="D50">
-        <v>142.5117553015826</v>
+        <v>140.66235059679</v>
       </c>
       <c r="E50">
-        <v>109.936</v>
+        <v>113.368</v>
       </c>
       <c r="F50">
-        <v>164.736</v>
+        <v>168.168</v>
       </c>
       <c r="G50">
         <v>3.31</v>
@@ -5381,37 +5381,37 @@
         <v>10.7</v>
       </c>
       <c r="M50">
-        <v>38.8447488</v>
+        <v>39.65401439999999</v>
       </c>
       <c r="N50">
-        <v>-28.1447488</v>
+        <v>-28.95401439999999</v>
       </c>
       <c r="O50">
-        <v>-4.503159807999999</v>
+        <v>-4.632642303999999</v>
       </c>
       <c r="P50">
-        <v>-23.641588992</v>
+        <v>-24.321372096</v>
       </c>
       <c r="Q50">
-        <v>-11.441588992</v>
+        <v>-12.121372096</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1579132336716711</v>
+        <v>0.1601115323711156</v>
       </c>
       <c r="T50">
-        <v>1.543280861470345</v>
+        <v>1.573541270518783</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04407288122300845</v>
+        <v>0.04317343466743686</v>
       </c>
       <c r="W50">
-        <v>0.2254076146076146</v>
+        <v>0.2256197041054184</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2754555076438028</v>
+        <v>0.2698339666714803</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.192210536520924</v>
+        <v>0.194110536520924</v>
       </c>
       <c r="C51">
-        <v>-24.19564940320993</v>
+        <v>-29.42966881736126</v>
       </c>
       <c r="D51">
-        <v>140.66235059679</v>
+        <v>138.8603311826387</v>
       </c>
       <c r="E51">
-        <v>113.368</v>
+        <v>116.8</v>
       </c>
       <c r="F51">
-        <v>168.168</v>
+        <v>171.6</v>
       </c>
       <c r="G51">
         <v>3.31</v>
@@ -5463,37 +5463,37 @@
         <v>10.7</v>
       </c>
       <c r="M51">
-        <v>39.65401439999999</v>
+        <v>40.46328</v>
       </c>
       <c r="N51">
-        <v>-28.95401439999999</v>
+        <v>-29.76328</v>
       </c>
       <c r="O51">
-        <v>-4.632642303999999</v>
+        <v>-4.7621248</v>
       </c>
       <c r="P51">
-        <v>-24.321372096</v>
+        <v>-25.0011552</v>
       </c>
       <c r="Q51">
-        <v>-12.121372096</v>
+        <v>-12.8011552</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1601115323711156</v>
+        <v>0.1623977630185379</v>
       </c>
       <c r="T51">
-        <v>1.573541270518783</v>
+        <v>1.605012095929159</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04317343466743686</v>
+        <v>0.04230996597408811</v>
       </c>
       <c r="W51">
-        <v>0.2256197041054184</v>
+        <v>0.22582331002331</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2698339666714803</v>
+        <v>0.2644372873380507</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.194110536520924</v>
+        <v>0.196010536520924</v>
       </c>
       <c r="C52">
-        <v>-29.42966881736126</v>
+        <v>-34.61810105812003</v>
       </c>
       <c r="D52">
-        <v>138.8603311826387</v>
+        <v>137.10389894188</v>
       </c>
       <c r="E52">
-        <v>116.8</v>
+        <v>120.232</v>
       </c>
       <c r="F52">
-        <v>171.6</v>
+        <v>175.032</v>
       </c>
       <c r="G52">
         <v>3.31</v>
@@ -5545,37 +5545,37 @@
         <v>10.7</v>
       </c>
       <c r="M52">
-        <v>40.46328</v>
+        <v>41.2725456</v>
       </c>
       <c r="N52">
-        <v>-29.76328</v>
+        <v>-30.5725456</v>
       </c>
       <c r="O52">
-        <v>-4.7621248</v>
+        <v>-4.891607296</v>
       </c>
       <c r="P52">
-        <v>-25.0011552</v>
+        <v>-25.680938304</v>
       </c>
       <c r="Q52">
-        <v>-12.8011552</v>
+        <v>-13.480938304</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1623977630185379</v>
+        <v>0.1647773092025897</v>
       </c>
       <c r="T52">
-        <v>1.605012095929159</v>
+        <v>1.637767444825672</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04230996597408811</v>
+        <v>0.0414803587981256</v>
       </c>
       <c r="W52">
-        <v>0.22582331002331</v>
+        <v>0.226018931395402</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2644372873380507</v>
+        <v>0.2592522424882849</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.196010536520924</v>
+        <v>0.197910536520924</v>
       </c>
       <c r="C53">
-        <v>-34.61810105812003</v>
+        <v>-39.76265440220567</v>
       </c>
       <c r="D53">
-        <v>137.10389894188</v>
+        <v>135.3913455977943</v>
       </c>
       <c r="E53">
-        <v>120.232</v>
+        <v>123.664</v>
       </c>
       <c r="F53">
-        <v>175.032</v>
+        <v>178.464</v>
       </c>
       <c r="G53">
         <v>3.31</v>
@@ -5627,37 +5627,37 @@
         <v>10.7</v>
       </c>
       <c r="M53">
-        <v>41.2725456</v>
+        <v>42.0818112</v>
       </c>
       <c r="N53">
-        <v>-30.5725456</v>
+        <v>-31.3818112</v>
       </c>
       <c r="O53">
-        <v>-4.891607296</v>
+        <v>-5.021089792000001</v>
       </c>
       <c r="P53">
-        <v>-25.680938304</v>
+        <v>-26.360721408</v>
       </c>
       <c r="Q53">
-        <v>-13.480938304</v>
+        <v>-14.160721408</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1647773092025897</v>
+        <v>0.1672560031443103</v>
       </c>
       <c r="T53">
-        <v>1.637767444825672</v>
+        <v>1.671887599926207</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.0414803587981256</v>
+        <v>0.04068265959046933</v>
       </c>
       <c r="W53">
-        <v>0.226018931395402</v>
+        <v>0.2262070288685673</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2592522424882849</v>
+        <v>0.2542666224404333</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.197910536520924</v>
+        <v>0.199810536520924</v>
       </c>
       <c r="C54">
-        <v>-39.76265440220567</v>
+        <v>-44.86495282754009</v>
       </c>
       <c r="D54">
-        <v>135.3913455977943</v>
+        <v>133.7210471724599</v>
       </c>
       <c r="E54">
-        <v>123.664</v>
+        <v>127.096</v>
       </c>
       <c r="F54">
-        <v>178.464</v>
+        <v>181.896</v>
       </c>
       <c r="G54">
         <v>3.31</v>
@@ -5709,37 +5709,37 @@
         <v>10.7</v>
       </c>
       <c r="M54">
-        <v>42.0818112</v>
+        <v>42.89107680000001</v>
       </c>
       <c r="N54">
-        <v>-31.3818112</v>
+        <v>-32.1910768</v>
       </c>
       <c r="O54">
-        <v>-5.021089792000001</v>
+        <v>-5.150572288000001</v>
       </c>
       <c r="P54">
-        <v>-26.360721408</v>
+        <v>-27.04050451200001</v>
       </c>
       <c r="Q54">
-        <v>-14.160721408</v>
+        <v>-14.84050451200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1672560031443103</v>
+        <v>0.1698401734239765</v>
       </c>
       <c r="T54">
-        <v>1.671887599926207</v>
+        <v>1.707459676520382</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04068265959046933</v>
+        <v>0.03991506223970576</v>
       </c>
       <c r="W54">
-        <v>0.2262070288685673</v>
+        <v>0.2263880283238774</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2542666224404333</v>
+        <v>0.249469138998161</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.199810536520924</v>
+        <v>0.201710536520924</v>
       </c>
       <c r="C55">
-        <v>-44.86495282754009</v>
+        <v>-49.92654114977367</v>
       </c>
       <c r="D55">
-        <v>133.7210471724599</v>
+        <v>132.0914588502263</v>
       </c>
       <c r="E55">
-        <v>127.096</v>
+        <v>130.528</v>
       </c>
       <c r="F55">
-        <v>181.896</v>
+        <v>185.328</v>
       </c>
       <c r="G55">
         <v>3.31</v>
@@ -5791,37 +5791,37 @@
         <v>10.7</v>
       </c>
       <c r="M55">
-        <v>42.89107680000001</v>
+        <v>43.7003424</v>
       </c>
       <c r="N55">
-        <v>-32.1910768</v>
+        <v>-33.00034240000001</v>
       </c>
       <c r="O55">
-        <v>-5.150572288000001</v>
+        <v>-5.280054784000002</v>
       </c>
       <c r="P55">
-        <v>-27.04050451200001</v>
+        <v>-27.72028761600001</v>
       </c>
       <c r="Q55">
-        <v>-14.84050451200001</v>
+        <v>-15.52028761600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1698401734239765</v>
+        <v>0.1725366989331934</v>
       </c>
       <c r="T55">
-        <v>1.707459676520382</v>
+        <v>1.74457836514039</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03991506223970576</v>
+        <v>0.03917589442045195</v>
       </c>
       <c r="W55">
-        <v>0.2263880283238774</v>
+        <v>0.2265623240956574</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.249469138998161</v>
+        <v>0.2448493401278246</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.201710536520924</v>
+        <v>0.203610536520924</v>
       </c>
       <c r="C56">
-        <v>-49.92654114977367</v>
+        <v>-54.9488897877568</v>
       </c>
       <c r="D56">
-        <v>132.0914588502263</v>
+        <v>130.5011102122432</v>
       </c>
       <c r="E56">
-        <v>130.528</v>
+        <v>133.96</v>
       </c>
       <c r="F56">
-        <v>185.328</v>
+        <v>188.76</v>
       </c>
       <c r="G56">
         <v>3.31</v>
@@ -5873,37 +5873,37 @@
         <v>10.7</v>
       </c>
       <c r="M56">
-        <v>43.7003424</v>
+        <v>44.50960800000001</v>
       </c>
       <c r="N56">
-        <v>-33.00034240000001</v>
+        <v>-33.80960800000001</v>
       </c>
       <c r="O56">
-        <v>-5.280054784000002</v>
+        <v>-5.409537280000002</v>
       </c>
       <c r="P56">
-        <v>-27.72028761600001</v>
+        <v>-28.40007072000001</v>
       </c>
       <c r="Q56">
-        <v>-15.52028761600001</v>
+        <v>-16.20007072000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1725366989331934</v>
+        <v>0.1753530700205977</v>
       </c>
       <c r="T56">
-        <v>1.74457836514039</v>
+        <v>1.783346773254621</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03917589442045195</v>
+        <v>0.03846360543098919</v>
       </c>
       <c r="W56">
-        <v>0.2265623240956574</v>
+        <v>0.2267302818393728</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2448493401278246</v>
+        <v>0.2403975339436824</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.203610536520924</v>
+        <v>0.205510536520924</v>
       </c>
       <c r="C57">
-        <v>-54.9488897877568</v>
+        <v>-59.93339918885556</v>
       </c>
       <c r="D57">
-        <v>130.5011102122432</v>
+        <v>128.9486008111444</v>
       </c>
       <c r="E57">
-        <v>133.96</v>
+        <v>137.392</v>
       </c>
       <c r="F57">
-        <v>188.76</v>
+        <v>192.192</v>
       </c>
       <c r="G57">
         <v>3.31</v>
@@ -5955,37 +5955,37 @@
         <v>10.7</v>
       </c>
       <c r="M57">
-        <v>44.50960800000001</v>
+        <v>45.3188736</v>
       </c>
       <c r="N57">
-        <v>-33.80960800000001</v>
+        <v>-34.6188736</v>
       </c>
       <c r="O57">
-        <v>-5.409537280000002</v>
+        <v>-5.539019776</v>
       </c>
       <c r="P57">
-        <v>-28.40007072000001</v>
+        <v>-29.079853824</v>
       </c>
       <c r="Q57">
-        <v>-16.20007072000001</v>
+        <v>-16.879853824</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1753530700205977</v>
+        <v>0.1782974579756113</v>
       </c>
       <c r="T57">
-        <v>1.783346773254621</v>
+        <v>1.823877381737681</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03846360543098919</v>
+        <v>0.03777675533400723</v>
       </c>
       <c r="W57">
-        <v>0.2267302818393728</v>
+        <v>0.2268922410922411</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2403975339436824</v>
+        <v>0.2361047208375453</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.205510536520924</v>
+        <v>0.207410536520924</v>
       </c>
       <c r="C58">
-        <v>-59.93339918885556</v>
+        <v>-64.88140394210663</v>
       </c>
       <c r="D58">
-        <v>128.9486008111444</v>
+        <v>127.4325960578934</v>
       </c>
       <c r="E58">
-        <v>137.392</v>
+        <v>140.824</v>
       </c>
       <c r="F58">
-        <v>192.192</v>
+        <v>195.624</v>
       </c>
       <c r="G58">
         <v>3.31</v>
@@ -6037,37 +6037,37 @@
         <v>10.7</v>
       </c>
       <c r="M58">
-        <v>45.3188736</v>
+        <v>46.12813920000001</v>
       </c>
       <c r="N58">
-        <v>-34.6188736</v>
+        <v>-35.4281392</v>
       </c>
       <c r="O58">
-        <v>-5.539019776</v>
+        <v>-5.668502272</v>
       </c>
       <c r="P58">
-        <v>-29.079853824</v>
+        <v>-29.759636928</v>
       </c>
       <c r="Q58">
-        <v>-16.879853824</v>
+        <v>-17.559636928</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1782974579756113</v>
+        <v>0.1813787942076023</v>
       </c>
       <c r="T58">
-        <v>1.823877381737681</v>
+        <v>1.866293134801347</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03777675533400723</v>
+        <v>0.03711400524042816</v>
       </c>
       <c r="W58">
-        <v>0.2268922410922411</v>
+        <v>0.2270485175643071</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2361047208375453</v>
+        <v>0.2319625327526761</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.207410536520924</v>
+        <v>0.209310536520924</v>
       </c>
       <c r="C59">
-        <v>-64.88140394210663</v>
+        <v>-69.79417660460118</v>
       </c>
       <c r="D59">
-        <v>127.4325960578934</v>
+        <v>125.9518233953988</v>
       </c>
       <c r="E59">
-        <v>140.824</v>
+        <v>144.256</v>
       </c>
       <c r="F59">
-        <v>195.624</v>
+        <v>199.056</v>
       </c>
       <c r="G59">
         <v>3.31</v>
@@ -6119,37 +6119,37 @@
         <v>10.7</v>
       </c>
       <c r="M59">
-        <v>46.12813920000001</v>
+        <v>46.9374048</v>
       </c>
       <c r="N59">
-        <v>-35.4281392</v>
+        <v>-36.23740480000001</v>
       </c>
       <c r="O59">
-        <v>-5.668502272</v>
+        <v>-5.797984768000001</v>
       </c>
       <c r="P59">
-        <v>-29.759636928</v>
+        <v>-30.43942003200001</v>
       </c>
       <c r="Q59">
-        <v>-17.559636928</v>
+        <v>-18.23942003200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1813787942076023</v>
+        <v>0.1846068607363547</v>
       </c>
       <c r="T59">
-        <v>1.866293134801347</v>
+        <v>1.910728685629951</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03711400524042816</v>
+        <v>0.03647410859835182</v>
       </c>
       <c r="W59">
-        <v>0.2270485175643071</v>
+        <v>0.2271994051925087</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2319625327526761</v>
+        <v>0.2279631787396987</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.209310536520924</v>
+        <v>0.211210536520924</v>
       </c>
       <c r="C60">
-        <v>-69.79417660460112</v>
+        <v>-74.6729312641568</v>
       </c>
       <c r="D60">
-        <v>125.9518233953989</v>
+        <v>124.5050687358432</v>
       </c>
       <c r="E60">
-        <v>144.256</v>
+        <v>147.688</v>
       </c>
       <c r="F60">
-        <v>199.056</v>
+        <v>202.488</v>
       </c>
       <c r="G60">
         <v>3.31</v>
@@ -6201,37 +6201,37 @@
         <v>10.7</v>
       </c>
       <c r="M60">
-        <v>46.9374048</v>
+        <v>47.74667039999999</v>
       </c>
       <c r="N60">
-        <v>-36.23740479999999</v>
+        <v>-37.0466704</v>
       </c>
       <c r="O60">
-        <v>-5.797984767999999</v>
+        <v>-5.927467264</v>
       </c>
       <c r="P60">
-        <v>-30.43942003199999</v>
+        <v>-31.119203136</v>
       </c>
       <c r="Q60">
-        <v>-18.23942003199999</v>
+        <v>-18.919203136</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1846068607363547</v>
+        <v>0.1879923939250462</v>
       </c>
       <c r="T60">
-        <v>1.910728685629951</v>
+        <v>1.957331824303852</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03647410859835182</v>
+        <v>0.03585590336787128</v>
       </c>
       <c r="W60">
-        <v>0.2271994051925087</v>
+        <v>0.227345177985856</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.227963178739699</v>
+        <v>0.2240993960491955</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.211210536520924</v>
+        <v>0.2131105365209239</v>
       </c>
       <c r="C61">
-        <v>-74.6729312641568</v>
+        <v>-79.51882685924093</v>
       </c>
       <c r="D61">
-        <v>124.5050687358432</v>
+        <v>123.0911731407591</v>
       </c>
       <c r="E61">
-        <v>147.688</v>
+        <v>151.12</v>
       </c>
       <c r="F61">
-        <v>202.488</v>
+        <v>205.92</v>
       </c>
       <c r="G61">
         <v>3.31</v>
@@ -6283,37 +6283,37 @@
         <v>10.7</v>
       </c>
       <c r="M61">
-        <v>47.74667039999999</v>
+        <v>48.555936</v>
       </c>
       <c r="N61">
-        <v>-37.0466704</v>
+        <v>-37.855936</v>
       </c>
       <c r="O61">
-        <v>-5.927467264</v>
+        <v>-6.05694976</v>
       </c>
       <c r="P61">
-        <v>-31.119203136</v>
+        <v>-31.79898624</v>
       </c>
       <c r="Q61">
-        <v>-18.919203136</v>
+        <v>-19.59898624</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1879923939250462</v>
+        <v>0.1915472037731724</v>
       </c>
       <c r="T61">
-        <v>1.957331824303852</v>
+        <v>2.006265119911448</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03585590336787128</v>
+        <v>0.03525830497840676</v>
       </c>
       <c r="W61">
-        <v>0.227345177985856</v>
+        <v>0.2274860916860917</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2240993960491955</v>
+        <v>0.2203644061150422</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2131105365209239</v>
+        <v>0.2150105365209239</v>
       </c>
       <c r="C62">
-        <v>-79.51882685924093</v>
+        <v>-84.33297027522451</v>
       </c>
       <c r="D62">
-        <v>123.0911731407591</v>
+        <v>121.7090297247755</v>
       </c>
       <c r="E62">
-        <v>151.12</v>
+        <v>154.552</v>
       </c>
       <c r="F62">
-        <v>205.92</v>
+        <v>209.352</v>
       </c>
       <c r="G62">
         <v>3.31</v>
@@ -6365,37 +6365,37 @@
         <v>10.7</v>
       </c>
       <c r="M62">
-        <v>48.555936</v>
+        <v>49.3652016</v>
       </c>
       <c r="N62">
-        <v>-37.855936</v>
+        <v>-38.6652016</v>
       </c>
       <c r="O62">
-        <v>-6.05694976</v>
+        <v>-6.186432256000001</v>
       </c>
       <c r="P62">
-        <v>-31.79898624</v>
+        <v>-32.478769344</v>
       </c>
       <c r="Q62">
-        <v>-19.59898624</v>
+        <v>-20.278769344</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1915472037731724</v>
+        <v>0.1952843115622281</v>
       </c>
       <c r="T62">
-        <v>2.006265119911448</v>
+        <v>2.057707815293793</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03525830497840676</v>
+        <v>0.03468029997876075</v>
       </c>
       <c r="W62">
-        <v>0.2274860916860917</v>
+        <v>0.2276223852650082</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2203644061150422</v>
+        <v>0.2167518748672546</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2150105365209239</v>
+        <v>0.216910536520924</v>
       </c>
       <c r="C63">
-        <v>-84.33297027522451</v>
+        <v>-89.11641923435278</v>
       </c>
       <c r="D63">
-        <v>121.7090297247755</v>
+        <v>120.3575807656472</v>
       </c>
       <c r="E63">
-        <v>154.552</v>
+        <v>157.984</v>
       </c>
       <c r="F63">
-        <v>209.352</v>
+        <v>212.784</v>
       </c>
       <c r="G63">
         <v>3.31</v>
@@ -6447,37 +6447,37 @@
         <v>10.7</v>
       </c>
       <c r="M63">
-        <v>49.3652016</v>
+        <v>50.1744672</v>
       </c>
       <c r="N63">
-        <v>-38.6652016</v>
+        <v>-39.47446720000001</v>
       </c>
       <c r="O63">
-        <v>-6.186432256000001</v>
+        <v>-6.315914752000001</v>
       </c>
       <c r="P63">
-        <v>-32.478769344</v>
+        <v>-33.15855244800001</v>
       </c>
       <c r="Q63">
-        <v>-20.278769344</v>
+        <v>-20.95855244800001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1952843115622281</v>
+        <v>0.1992181092349183</v>
       </c>
       <c r="T63">
-        <v>2.057707815293793</v>
+        <v>2.111858020959419</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03468029997876075</v>
+        <v>0.03412094030168396</v>
       </c>
       <c r="W63">
-        <v>0.2276223852650082</v>
+        <v>0.2277542822768629</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2167518748672546</v>
+        <v>0.2132558768855246</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.216910536520924</v>
+        <v>0.218810536520924</v>
       </c>
       <c r="C64">
-        <v>-89.11641923435278</v>
+        <v>-93.87018499528997</v>
       </c>
       <c r="D64">
-        <v>120.3575807656472</v>
+        <v>119.03581500471</v>
       </c>
       <c r="E64">
-        <v>157.984</v>
+        <v>161.416</v>
       </c>
       <c r="F64">
-        <v>212.784</v>
+        <v>216.216</v>
       </c>
       <c r="G64">
         <v>3.31</v>
@@ -6529,37 +6529,37 @@
         <v>10.7</v>
       </c>
       <c r="M64">
-        <v>50.1744672</v>
+        <v>50.98373280000001</v>
       </c>
       <c r="N64">
-        <v>-39.47446720000001</v>
+        <v>-40.28373280000001</v>
       </c>
       <c r="O64">
-        <v>-6.315914752000001</v>
+        <v>-6.445397248000002</v>
       </c>
       <c r="P64">
-        <v>-33.15855244800001</v>
+        <v>-33.83833555200001</v>
       </c>
       <c r="Q64">
-        <v>-20.95855244800001</v>
+        <v>-21.63833555200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1992181092349183</v>
+        <v>0.2033645446196458</v>
       </c>
       <c r="T64">
-        <v>2.111858020959419</v>
+        <v>2.168935264769133</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03412094030168396</v>
+        <v>0.0335793380746731</v>
       </c>
       <c r="W64">
-        <v>0.2277542822768629</v>
+        <v>0.2278819920819921</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2132558768855246</v>
+        <v>0.2098708629667068</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.218810536520924</v>
+        <v>0.220710536520924</v>
       </c>
       <c r="C65">
-        <v>-93.87018499528997</v>
+        <v>-98.59523487671832</v>
       </c>
       <c r="D65">
-        <v>119.03581500471</v>
+        <v>117.7427651232817</v>
       </c>
       <c r="E65">
-        <v>161.416</v>
+        <v>164.848</v>
       </c>
       <c r="F65">
-        <v>216.216</v>
+        <v>219.648</v>
       </c>
       <c r="G65">
         <v>3.31</v>
@@ -6611,37 +6611,37 @@
         <v>10.7</v>
       </c>
       <c r="M65">
-        <v>50.98373280000001</v>
+        <v>51.7929984</v>
       </c>
       <c r="N65">
-        <v>-40.28373280000001</v>
+        <v>-41.0929984</v>
       </c>
       <c r="O65">
-        <v>-6.445397248000002</v>
+        <v>-6.574879744</v>
       </c>
       <c r="P65">
-        <v>-33.83833555200001</v>
+        <v>-34.518118656</v>
       </c>
       <c r="Q65">
-        <v>-21.63833555200001</v>
+        <v>-22.318118656</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2033645446196458</v>
+        <v>0.2077413375257471</v>
       </c>
       <c r="T65">
-        <v>2.168935264769133</v>
+        <v>2.229183466568276</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0335793380746731</v>
+        <v>0.03305466091725633</v>
       </c>
       <c r="W65">
-        <v>0.2278819920819921</v>
+        <v>0.228005710955711</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2098708629667068</v>
+        <v>0.2065916307328521</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.220710536520924</v>
+        <v>0.222610536520924</v>
       </c>
       <c r="C66">
-        <v>-98.59523487671832</v>
+        <v>-103.2924946182257</v>
       </c>
       <c r="D66">
-        <v>117.7427651232817</v>
+        <v>116.4775053817743</v>
       </c>
       <c r="E66">
-        <v>164.848</v>
+        <v>168.28</v>
       </c>
       <c r="F66">
-        <v>219.648</v>
+        <v>223.08</v>
       </c>
       <c r="G66">
         <v>3.31</v>
@@ -6693,37 +6693,37 @@
         <v>10.7</v>
       </c>
       <c r="M66">
-        <v>51.7929984</v>
+        <v>52.60226400000001</v>
       </c>
       <c r="N66">
-        <v>-41.0929984</v>
+        <v>-41.902264</v>
       </c>
       <c r="O66">
-        <v>-6.574879744</v>
+        <v>-6.704362240000001</v>
       </c>
       <c r="P66">
-        <v>-34.518118656</v>
+        <v>-35.19790176</v>
       </c>
       <c r="Q66">
-        <v>-22.318118656</v>
+        <v>-22.99790176</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2077413375257471</v>
+        <v>0.2123682328836256</v>
       </c>
       <c r="T66">
-        <v>2.229183466568276</v>
+        <v>2.292874422755941</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03305466091725633</v>
+        <v>0.03254612767237547</v>
       </c>
       <c r="W66">
-        <v>0.228005710955711</v>
+        <v>0.2281256230948539</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2065916307328521</v>
+        <v>0.2034132979523467</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.222610536520924</v>
+        <v>0.224510536520924</v>
       </c>
       <c r="C67">
-        <v>-103.2924946182257</v>
+        <v>-107.9628505905914</v>
       </c>
       <c r="D67">
-        <v>116.4775053817743</v>
+        <v>115.2391494094086</v>
       </c>
       <c r="E67">
-        <v>168.28</v>
+        <v>171.712</v>
       </c>
       <c r="F67">
-        <v>223.08</v>
+        <v>226.512</v>
       </c>
       <c r="G67">
         <v>3.31</v>
@@ -6775,37 +6775,37 @@
         <v>10.7</v>
       </c>
       <c r="M67">
-        <v>52.60226400000001</v>
+        <v>53.4115296</v>
       </c>
       <c r="N67">
-        <v>-41.902264</v>
+        <v>-42.71152960000001</v>
       </c>
       <c r="O67">
-        <v>-6.704362240000001</v>
+        <v>-6.833844736000001</v>
       </c>
       <c r="P67">
-        <v>-35.19790176</v>
+        <v>-35.877684864</v>
       </c>
       <c r="Q67">
-        <v>-22.99790176</v>
+        <v>-23.677684864</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2123682328836256</v>
+        <v>0.2172672985566735</v>
       </c>
       <c r="T67">
-        <v>2.292874422755941</v>
+        <v>2.360311905778175</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03254612767237547</v>
+        <v>0.03205300452582432</v>
       </c>
       <c r="W67">
-        <v>0.2281256230948539</v>
+        <v>0.2282419015328107</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2034132979523467</v>
+        <v>0.200331278286402</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.224510536520924</v>
+        <v>0.226410536520924</v>
       </c>
       <c r="C68">
-        <v>-107.9628505905914</v>
+        <v>-112.607151866561</v>
       </c>
       <c r="D68">
-        <v>115.2391494094086</v>
+        <v>114.026848133439</v>
       </c>
       <c r="E68">
-        <v>171.712</v>
+        <v>175.144</v>
       </c>
       <c r="F68">
-        <v>226.512</v>
+        <v>229.944</v>
       </c>
       <c r="G68">
         <v>3.31</v>
@@ -6857,37 +6857,37 @@
         <v>10.7</v>
       </c>
       <c r="M68">
-        <v>53.4115296</v>
+        <v>54.2207952</v>
       </c>
       <c r="N68">
-        <v>-42.71152960000001</v>
+        <v>-43.52079520000001</v>
       </c>
       <c r="O68">
-        <v>-6.833844736000001</v>
+        <v>-6.963327232000002</v>
       </c>
       <c r="P68">
-        <v>-35.877684864</v>
+        <v>-36.557467968</v>
       </c>
       <c r="Q68">
-        <v>-23.677684864</v>
+        <v>-24.35746796800001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2172672985566735</v>
+        <v>0.2224632773008151</v>
       </c>
       <c r="T68">
-        <v>2.360311905778175</v>
+        <v>2.431836508983574</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03205300452582432</v>
+        <v>0.03157460147320008</v>
       </c>
       <c r="W68">
-        <v>0.2282419015328107</v>
+        <v>0.2283547089726194</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.200331278286402</v>
+        <v>0.1973412592075005</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.226410536520924</v>
+        <v>0.228310536520924</v>
       </c>
       <c r="C69">
-        <v>-112.607151866561</v>
+        <v>-117.2262121622755</v>
       </c>
       <c r="D69">
-        <v>114.026848133439</v>
+        <v>112.8397878377245</v>
       </c>
       <c r="E69">
-        <v>175.144</v>
+        <v>178.576</v>
       </c>
       <c r="F69">
-        <v>229.944</v>
+        <v>233.376</v>
       </c>
       <c r="G69">
         <v>3.31</v>
@@ -6939,37 +6939,37 @@
         <v>10.7</v>
       </c>
       <c r="M69">
-        <v>54.2207952</v>
+        <v>55.0300608</v>
       </c>
       <c r="N69">
-        <v>-43.52079520000001</v>
+        <v>-44.3300608</v>
       </c>
       <c r="O69">
-        <v>-6.963327232000002</v>
+        <v>-7.092809728</v>
       </c>
       <c r="P69">
-        <v>-36.557467968</v>
+        <v>-37.237251072</v>
       </c>
       <c r="Q69">
-        <v>-24.35746796800001</v>
+        <v>-25.037251072</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2224632773008151</v>
+        <v>0.2279840047164655</v>
       </c>
       <c r="T69">
-        <v>2.431836508983574</v>
+        <v>2.507831399889311</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03157460147320008</v>
+        <v>0.0311102690985942</v>
       </c>
       <c r="W69">
-        <v>0.2283547089726194</v>
+        <v>0.2284641985465515</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1973412592075005</v>
+        <v>0.1944391818662138</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.228310536520924</v>
+        <v>0.230210536520924</v>
       </c>
       <c r="C70">
-        <v>-117.2262121622755</v>
+        <v>-121.8208116586841</v>
       </c>
       <c r="D70">
-        <v>112.8397878377245</v>
+        <v>111.6771883413159</v>
       </c>
       <c r="E70">
-        <v>178.576</v>
+        <v>182.008</v>
       </c>
       <c r="F70">
-        <v>233.376</v>
+        <v>236.808</v>
       </c>
       <c r="G70">
         <v>3.31</v>
@@ -7021,37 +7021,37 @@
         <v>10.7</v>
       </c>
       <c r="M70">
-        <v>55.0300608</v>
+        <v>55.8393264</v>
       </c>
       <c r="N70">
-        <v>-44.3300608</v>
+        <v>-45.1393264</v>
       </c>
       <c r="O70">
-        <v>-7.092809728</v>
+        <v>-7.222292224</v>
       </c>
       <c r="P70">
-        <v>-37.237251072</v>
+        <v>-37.917034176</v>
       </c>
       <c r="Q70">
-        <v>-25.037251072</v>
+        <v>-25.717034176</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2279840047164655</v>
+        <v>0.233860908094416</v>
       </c>
       <c r="T70">
-        <v>2.507831399889311</v>
+        <v>2.588729186982515</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0311102690985942</v>
+        <v>0.03065939563339718</v>
       </c>
       <c r="W70">
-        <v>0.2284641985465515</v>
+        <v>0.228570514509645</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1944391818662138</v>
+        <v>0.1916212227087324</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.230210536520924</v>
+        <v>0.232110536520924</v>
       </c>
       <c r="C71">
-        <v>-121.8208116586841</v>
+        <v>-126.3916987115088</v>
       </c>
       <c r="D71">
-        <v>111.6771883413159</v>
+        <v>110.5383012884912</v>
       </c>
       <c r="E71">
-        <v>182.008</v>
+        <v>185.44</v>
       </c>
       <c r="F71">
-        <v>236.808</v>
+        <v>240.24</v>
       </c>
       <c r="G71">
         <v>3.31</v>
@@ -7103,37 +7103,37 @@
         <v>10.7</v>
       </c>
       <c r="M71">
-        <v>55.8393264</v>
+        <v>56.64859200000001</v>
       </c>
       <c r="N71">
-        <v>-45.1393264</v>
+        <v>-45.948592</v>
       </c>
       <c r="O71">
-        <v>-7.222292224</v>
+        <v>-7.351774720000001</v>
       </c>
       <c r="P71">
-        <v>-37.917034176</v>
+        <v>-38.59681728</v>
       </c>
       <c r="Q71">
-        <v>-25.717034176</v>
+        <v>-26.39681728</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.233860908094416</v>
+        <v>0.2401296050308966</v>
       </c>
       <c r="T71">
-        <v>2.588729186982515</v>
+        <v>2.675020159881932</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03065939563339718</v>
+        <v>0.03022140426720579</v>
       </c>
       <c r="W71">
-        <v>0.228570514509645</v>
+        <v>0.2286737928737929</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1916212227087324</v>
+        <v>0.1888837766700362</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.232110536520924</v>
+        <v>0.234010536520924</v>
       </c>
       <c r="C72">
-        <v>-126.3916987115088</v>
+        <v>-130.9395914576346</v>
       </c>
       <c r="D72">
-        <v>110.5383012884912</v>
+        <v>109.4224085423654</v>
       </c>
       <c r="E72">
-        <v>185.44</v>
+        <v>188.872</v>
       </c>
       <c r="F72">
-        <v>240.24</v>
+        <v>243.672</v>
       </c>
       <c r="G72">
         <v>3.31</v>
@@ -7185,37 +7185,37 @@
         <v>10.7</v>
       </c>
       <c r="M72">
-        <v>56.64859200000001</v>
+        <v>57.45785760000001</v>
       </c>
       <c r="N72">
-        <v>-45.948592</v>
+        <v>-46.75785760000001</v>
       </c>
       <c r="O72">
-        <v>-7.351774720000001</v>
+        <v>-7.481257216000001</v>
       </c>
       <c r="P72">
-        <v>-38.59681728</v>
+        <v>-39.27660038400001</v>
       </c>
       <c r="Q72">
-        <v>-26.39681728</v>
+        <v>-27.07660038400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2401296050308966</v>
+        <v>0.246830625894031</v>
       </c>
       <c r="T72">
-        <v>2.675020159881932</v>
+        <v>2.767262234360619</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03022140426720579</v>
+        <v>0.02979575068597753</v>
       </c>
       <c r="W72">
-        <v>0.2286737928737929</v>
+        <v>0.2287741619882465</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1888837766700362</v>
+        <v>0.1862234417873596</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.234010536520924</v>
+        <v>0.235910536520924</v>
       </c>
       <c r="C73">
-        <v>-130.9395914576345</v>
+        <v>-135.4651793251729</v>
       </c>
       <c r="D73">
-        <v>109.4224085423654</v>
+        <v>108.3288206748271</v>
       </c>
       <c r="E73">
-        <v>188.872</v>
+        <v>192.304</v>
       </c>
       <c r="F73">
-        <v>243.672</v>
+        <v>247.104</v>
       </c>
       <c r="G73">
         <v>3.31</v>
@@ -7267,37 +7267,37 @@
         <v>10.7</v>
       </c>
       <c r="M73">
-        <v>57.4578576</v>
+        <v>58.2671232</v>
       </c>
       <c r="N73">
-        <v>-46.75785759999999</v>
+        <v>-47.5671232</v>
       </c>
       <c r="O73">
-        <v>-7.481257215999999</v>
+        <v>-7.610739712</v>
       </c>
       <c r="P73">
-        <v>-39.27660038399999</v>
+        <v>-39.956383488</v>
       </c>
       <c r="Q73">
-        <v>-27.07660038399999</v>
+        <v>-27.756383488</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2468306258940309</v>
+        <v>0.254010291104532</v>
       </c>
       <c r="T73">
-        <v>2.767262234360619</v>
+        <v>2.866093028444926</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02979575068597754</v>
+        <v>0.02938192081533897</v>
       </c>
       <c r="W73">
-        <v>0.2287741619882465</v>
+        <v>0.2288717430717431</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1862234417873597</v>
+        <v>0.1836370050958686</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.235910536520924</v>
+        <v>0.237810536520924</v>
       </c>
       <c r="C74">
-        <v>-135.4651793251729</v>
+        <v>-139.9691244538703</v>
       </c>
       <c r="D74">
-        <v>108.3288206748271</v>
+        <v>107.2568755461297</v>
       </c>
       <c r="E74">
-        <v>192.304</v>
+        <v>195.736</v>
       </c>
       <c r="F74">
-        <v>247.104</v>
+        <v>250.536</v>
       </c>
       <c r="G74">
         <v>3.31</v>
@@ -7349,37 +7349,37 @@
         <v>10.7</v>
       </c>
       <c r="M74">
-        <v>58.2671232</v>
+        <v>59.0763888</v>
       </c>
       <c r="N74">
-        <v>-47.5671232</v>
+        <v>-48.3763888</v>
       </c>
       <c r="O74">
-        <v>-7.610739712</v>
+        <v>-7.740222208</v>
       </c>
       <c r="P74">
-        <v>-39.956383488</v>
+        <v>-40.636166592</v>
       </c>
       <c r="Q74">
-        <v>-27.756383488</v>
+        <v>-28.436166592</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.254010291104532</v>
+        <v>0.2617217833676628</v>
       </c>
       <c r="T74">
-        <v>2.866093028444926</v>
+        <v>2.972244622091035</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02938192081533897</v>
+        <v>0.02897942874937542</v>
       </c>
       <c r="W74">
-        <v>0.2288717430717431</v>
+        <v>0.2289666507008973</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1836370050958686</v>
+        <v>0.1811214296835963</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.237810536520924</v>
+        <v>0.239710536520924</v>
       </c>
       <c r="C75">
-        <v>-139.9691244538703</v>
+        <v>-144.4520630320102</v>
       </c>
       <c r="D75">
-        <v>107.2568755461297</v>
+        <v>106.2059369679898</v>
       </c>
       <c r="E75">
-        <v>195.736</v>
+        <v>199.168</v>
       </c>
       <c r="F75">
-        <v>250.536</v>
+        <v>253.968</v>
       </c>
       <c r="G75">
         <v>3.31</v>
@@ -7431,37 +7431,37 @@
         <v>10.7</v>
       </c>
       <c r="M75">
-        <v>59.0763888</v>
+        <v>59.8856544</v>
       </c>
       <c r="N75">
-        <v>-48.3763888</v>
+        <v>-49.1856544</v>
       </c>
       <c r="O75">
-        <v>-7.740222208</v>
+        <v>-7.869704704000001</v>
       </c>
       <c r="P75">
-        <v>-40.636166592</v>
+        <v>-41.315949696</v>
       </c>
       <c r="Q75">
-        <v>-28.436166592</v>
+        <v>-29.115949696</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2617217833676628</v>
+        <v>0.2700264673433421</v>
       </c>
       <c r="T75">
-        <v>2.972244622091035</v>
+        <v>3.08656172294069</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02897942874937542</v>
+        <v>0.02858781484735683</v>
       </c>
       <c r="W75">
-        <v>0.2289666507008973</v>
+        <v>0.2290589932589933</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1811214296835963</v>
+        <v>0.1786738427959801</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.239710536520924</v>
+        <v>0.241610536520924</v>
       </c>
       <c r="C76">
-        <v>-144.4520630320102</v>
+        <v>-148.914606555482</v>
       </c>
       <c r="D76">
-        <v>106.2059369679898</v>
+        <v>105.175393444518</v>
       </c>
       <c r="E76">
-        <v>199.168</v>
+        <v>202.6</v>
       </c>
       <c r="F76">
-        <v>253.968</v>
+        <v>257.4</v>
       </c>
       <c r="G76">
         <v>3.31</v>
@@ -7513,37 +7513,37 @@
         <v>10.7</v>
       </c>
       <c r="M76">
-        <v>59.8856544</v>
+        <v>60.69492</v>
       </c>
       <c r="N76">
-        <v>-49.1856544</v>
+        <v>-49.99491999999999</v>
       </c>
       <c r="O76">
-        <v>-7.869704704000001</v>
+        <v>-7.999187199999999</v>
       </c>
       <c r="P76">
-        <v>-41.315949696</v>
+        <v>-41.99573279999999</v>
       </c>
       <c r="Q76">
-        <v>-29.115949696</v>
+        <v>-29.79573279999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2700264673433421</v>
+        <v>0.2789955260370758</v>
       </c>
       <c r="T76">
-        <v>3.08656172294069</v>
+        <v>3.210024191858317</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02858781484735683</v>
+        <v>0.0282066439827254</v>
       </c>
       <c r="W76">
-        <v>0.2290589932589933</v>
+        <v>0.2291488733488733</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1786738427959801</v>
+        <v>0.1762915248920338</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.241610536520924</v>
+        <v>0.243510536520924</v>
       </c>
       <c r="C77">
-        <v>-148.914606555482</v>
+        <v>-153.3573430142516</v>
       </c>
       <c r="D77">
-        <v>105.175393444518</v>
+        <v>104.1646569857484</v>
       </c>
       <c r="E77">
-        <v>202.6</v>
+        <v>206.032</v>
       </c>
       <c r="F77">
-        <v>257.4</v>
+        <v>260.832</v>
       </c>
       <c r="G77">
         <v>3.31</v>
@@ -7595,37 +7595,37 @@
         <v>10.7</v>
       </c>
       <c r="M77">
-        <v>60.69492</v>
+        <v>61.5041856</v>
       </c>
       <c r="N77">
-        <v>-49.99491999999999</v>
+        <v>-50.8041856</v>
       </c>
       <c r="O77">
-        <v>-7.999187199999999</v>
+        <v>-8.128669695999999</v>
       </c>
       <c r="P77">
-        <v>-41.99573279999999</v>
+        <v>-42.67551590399999</v>
       </c>
       <c r="Q77">
-        <v>-29.79573279999999</v>
+        <v>-30.47551590399999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2789955260370758</v>
+        <v>0.2887120062886206</v>
       </c>
       <c r="T77">
-        <v>3.210024191858317</v>
+        <v>3.343775199852414</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0282066439827254</v>
+        <v>0.02783550393032113</v>
       </c>
       <c r="W77">
-        <v>0.2291488733488733</v>
+        <v>0.2292363881732303</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1762915248920338</v>
+        <v>0.1739718995645071</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.243510536520924</v>
+        <v>0.245410536520924</v>
       </c>
       <c r="C78">
-        <v>-153.3573430142516</v>
+        <v>-157.7808380110709</v>
       </c>
       <c r="D78">
-        <v>104.1646569857484</v>
+        <v>103.1731619889291</v>
       </c>
       <c r="E78">
-        <v>206.032</v>
+        <v>209.464</v>
       </c>
       <c r="F78">
-        <v>260.832</v>
+        <v>264.264</v>
       </c>
       <c r="G78">
         <v>3.31</v>
@@ -7677,37 +7677,37 @@
         <v>10.7</v>
       </c>
       <c r="M78">
-        <v>61.5041856</v>
+        <v>62.3134512</v>
       </c>
       <c r="N78">
-        <v>-50.8041856</v>
+        <v>-51.6134512</v>
       </c>
       <c r="O78">
-        <v>-8.128669695999999</v>
+        <v>-8.258152192000001</v>
       </c>
       <c r="P78">
-        <v>-42.67551590399999</v>
+        <v>-43.355299008</v>
       </c>
       <c r="Q78">
-        <v>-30.47551590399999</v>
+        <v>-31.155299008</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2887120062886206</v>
+        <v>0.2992733978663868</v>
       </c>
       <c r="T78">
-        <v>3.343775199852414</v>
+        <v>3.48915673028078</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02783550393032113</v>
+        <v>0.02747400387927799</v>
       </c>
       <c r="W78">
-        <v>0.2292363881732303</v>
+        <v>0.2293216298852662</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1739718995645071</v>
+        <v>0.1717125242454876</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.245410536520924</v>
+        <v>0.247310536520924</v>
       </c>
       <c r="C79">
-        <v>-157.7808380110709</v>
+        <v>-162.1856358168998</v>
       </c>
       <c r="D79">
-        <v>103.1731619889291</v>
+        <v>102.2003641831002</v>
       </c>
       <c r="E79">
-        <v>209.464</v>
+        <v>212.896</v>
       </c>
       <c r="F79">
-        <v>264.264</v>
+        <v>267.696</v>
       </c>
       <c r="G79">
         <v>3.31</v>
@@ -7759,37 +7759,37 @@
         <v>10.7</v>
       </c>
       <c r="M79">
-        <v>62.3134512</v>
+        <v>63.12271680000001</v>
       </c>
       <c r="N79">
-        <v>-51.6134512</v>
+        <v>-52.4227168</v>
       </c>
       <c r="O79">
-        <v>-8.258152192000001</v>
+        <v>-8.387634688</v>
       </c>
       <c r="P79">
-        <v>-43.355299008</v>
+        <v>-44.035082112</v>
       </c>
       <c r="Q79">
-        <v>-31.155299008</v>
+        <v>-31.83508211200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2992733978663868</v>
+        <v>0.3107949159512226</v>
       </c>
       <c r="T79">
-        <v>3.48915673028078</v>
+        <v>3.647754763475362</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02747400387927799</v>
+        <v>0.02712177306031289</v>
       </c>
       <c r="W79">
-        <v>0.2293216298852662</v>
+        <v>0.2294046859123782</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1717125242454876</v>
+        <v>0.1695110816269556</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.247310536520924</v>
+        <v>0.249210536520924</v>
       </c>
       <c r="C80">
-        <v>-162.1856358168998</v>
+        <v>-166.5722603671768</v>
       </c>
       <c r="D80">
-        <v>102.2003641831002</v>
+        <v>101.2457396328232</v>
       </c>
       <c r="E80">
-        <v>212.896</v>
+        <v>216.328</v>
       </c>
       <c r="F80">
-        <v>267.696</v>
+        <v>271.128</v>
       </c>
       <c r="G80">
         <v>3.31</v>
@@ -7841,37 +7841,37 @@
         <v>10.7</v>
       </c>
       <c r="M80">
-        <v>63.12271680000001</v>
+        <v>63.9319824</v>
       </c>
       <c r="N80">
-        <v>-52.4227168</v>
+        <v>-53.23198240000001</v>
       </c>
       <c r="O80">
-        <v>-8.387634688</v>
+        <v>-8.517117184000002</v>
       </c>
       <c r="P80">
-        <v>-44.035082112</v>
+        <v>-44.71486521600001</v>
       </c>
       <c r="Q80">
-        <v>-31.83508211200001</v>
+        <v>-32.514865216</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3107949159512226</v>
+        <v>0.3234137214727094</v>
       </c>
       <c r="T80">
-        <v>3.647754763475362</v>
+        <v>3.821457371259902</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02712177306031289</v>
+        <v>0.02677845947727096</v>
       </c>
       <c r="W80">
-        <v>0.2294046859123782</v>
+        <v>0.2294856392552595</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1695110816269556</v>
+        <v>0.1673653717329434</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.249210536520924</v>
+        <v>0.251110536520924</v>
       </c>
       <c r="C81">
-        <v>-166.5722603671768</v>
+        <v>-170.9412162027716</v>
       </c>
       <c r="D81">
-        <v>101.2457396328232</v>
+        <v>100.3087837972284</v>
       </c>
       <c r="E81">
-        <v>216.328</v>
+        <v>219.76</v>
       </c>
       <c r="F81">
-        <v>271.128</v>
+        <v>274.56</v>
       </c>
       <c r="G81">
         <v>3.31</v>
@@ -7923,37 +7923,37 @@
         <v>10.7</v>
       </c>
       <c r="M81">
-        <v>63.9319824</v>
+        <v>64.741248</v>
       </c>
       <c r="N81">
-        <v>-53.23198240000001</v>
+        <v>-54.041248</v>
       </c>
       <c r="O81">
-        <v>-8.517117184000002</v>
+        <v>-8.64659968</v>
       </c>
       <c r="P81">
-        <v>-44.71486521600001</v>
+        <v>-45.39464831999999</v>
       </c>
       <c r="Q81">
-        <v>-32.514865216</v>
+        <v>-33.19464832</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3234137214727094</v>
+        <v>0.3372944075463449</v>
       </c>
       <c r="T81">
-        <v>3.821457371259902</v>
+        <v>4.012530239822897</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02677845947727096</v>
+        <v>0.02644372873380507</v>
       </c>
       <c r="W81">
-        <v>0.2294856392552595</v>
+        <v>0.2295645687645688</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1673653717329434</v>
+        <v>0.1652733045862818</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.251110536520924</v>
+        <v>0.253010536520924</v>
       </c>
       <c r="C82">
-        <v>-170.9412162027716</v>
+        <v>-175.2929893591694</v>
       </c>
       <c r="D82">
-        <v>100.3087837972284</v>
+        <v>99.38901064083062</v>
       </c>
       <c r="E82">
-        <v>219.76</v>
+        <v>223.192</v>
       </c>
       <c r="F82">
-        <v>274.56</v>
+        <v>277.992</v>
       </c>
       <c r="G82">
         <v>3.31</v>
@@ -8005,37 +8005,37 @@
         <v>10.7</v>
       </c>
       <c r="M82">
-        <v>64.741248</v>
+        <v>65.5505136</v>
       </c>
       <c r="N82">
-        <v>-54.041248</v>
+        <v>-54.8505136</v>
       </c>
       <c r="O82">
-        <v>-8.64659968</v>
+        <v>-8.776082176000001</v>
       </c>
       <c r="P82">
-        <v>-45.39464831999999</v>
+        <v>-46.074431424</v>
       </c>
       <c r="Q82">
-        <v>-33.19464832</v>
+        <v>-33.87443142399999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3372944075463449</v>
+        <v>0.3526362184698367</v>
       </c>
       <c r="T82">
-        <v>4.012530239822897</v>
+        <v>4.22371604191884</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02644372873380507</v>
+        <v>0.02611726294696797</v>
       </c>
       <c r="W82">
-        <v>0.2295645687645688</v>
+        <v>0.229641549397105</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1652733045862818</v>
+        <v>0.1632328934185499</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.253010536520924</v>
+        <v>0.254910536520924</v>
       </c>
       <c r="C83">
-        <v>-175.2929893591694</v>
+        <v>-179.6280482071805</v>
       </c>
       <c r="D83">
-        <v>99.38901064083062</v>
+        <v>98.48595179281949</v>
       </c>
       <c r="E83">
-        <v>223.192</v>
+        <v>226.624</v>
       </c>
       <c r="F83">
-        <v>277.992</v>
+        <v>281.424</v>
       </c>
       <c r="G83">
         <v>3.31</v>
@@ -8087,37 +8087,37 @@
         <v>10.7</v>
       </c>
       <c r="M83">
-        <v>65.5505136</v>
+        <v>66.35977920000001</v>
       </c>
       <c r="N83">
-        <v>-54.8505136</v>
+        <v>-55.6597792</v>
       </c>
       <c r="O83">
-        <v>-8.776082176000001</v>
+        <v>-8.905564672000001</v>
       </c>
       <c r="P83">
-        <v>-46.074431424</v>
+        <v>-46.75421452800001</v>
       </c>
       <c r="Q83">
-        <v>-33.87443142399999</v>
+        <v>-34.554214528</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3526362184698367</v>
+        <v>0.3696826750514943</v>
       </c>
       <c r="T83">
-        <v>4.22371604191884</v>
+        <v>4.458366933136554</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02611726294696797</v>
+        <v>0.02579875974029763</v>
       </c>
       <c r="W83">
-        <v>0.229641549397105</v>
+        <v>0.2297166524532378</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1632328934185499</v>
+        <v>0.1612422483768602</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.254910536520924</v>
+        <v>0.256810536520924</v>
       </c>
       <c r="C84">
-        <v>-179.6280482071805</v>
+        <v>-183.9468442482294</v>
       </c>
       <c r="D84">
-        <v>98.48595179281949</v>
+        <v>97.5991557517706</v>
       </c>
       <c r="E84">
-        <v>226.624</v>
+        <v>230.056</v>
       </c>
       <c r="F84">
-        <v>281.424</v>
+        <v>284.856</v>
       </c>
       <c r="G84">
         <v>3.31</v>
@@ -8169,37 +8169,37 @@
         <v>10.7</v>
       </c>
       <c r="M84">
-        <v>66.35977920000001</v>
+        <v>67.16904479999999</v>
       </c>
       <c r="N84">
-        <v>-55.6597792</v>
+        <v>-56.46904479999999</v>
       </c>
       <c r="O84">
-        <v>-8.905564672000001</v>
+        <v>-9.035047167999998</v>
       </c>
       <c r="P84">
-        <v>-46.75421452800001</v>
+        <v>-47.43399763199999</v>
       </c>
       <c r="Q84">
-        <v>-34.554214528</v>
+        <v>-35.233997632</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3696826750514943</v>
+        <v>0.388734597113347</v>
       </c>
       <c r="T84">
-        <v>4.458366933136554</v>
+        <v>4.720623811556351</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02579875974029763</v>
+        <v>0.02548793130969164</v>
       </c>
       <c r="W84">
-        <v>0.2297166524532378</v>
+        <v>0.2297899457971747</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1612422483768602</v>
+        <v>0.1592995706855728</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.256810536520924</v>
+        <v>0.258710536520924</v>
       </c>
       <c r="C85">
-        <v>-183.9468442482294</v>
+        <v>-188.2498128670612</v>
       </c>
       <c r="D85">
-        <v>97.5991557517706</v>
+        <v>96.72818713293877</v>
       </c>
       <c r="E85">
-        <v>230.056</v>
+        <v>233.488</v>
       </c>
       <c r="F85">
-        <v>284.856</v>
+        <v>288.288</v>
       </c>
       <c r="G85">
         <v>3.31</v>
@@ -8251,37 +8251,37 @@
         <v>10.7</v>
       </c>
       <c r="M85">
-        <v>67.16904479999999</v>
+        <v>67.97831040000001</v>
       </c>
       <c r="N85">
-        <v>-56.46904479999999</v>
+        <v>-57.27831040000001</v>
       </c>
       <c r="O85">
-        <v>-9.035047167999998</v>
+        <v>-9.164529664000002</v>
       </c>
       <c r="P85">
-        <v>-47.43399763199999</v>
+        <v>-48.11378073600001</v>
       </c>
       <c r="Q85">
-        <v>-35.233997632</v>
+        <v>-35.91378073600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.388734597113347</v>
+        <v>0.4101680094329312</v>
       </c>
       <c r="T85">
-        <v>4.720623811556351</v>
+        <v>5.015662799778625</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02548793130969164</v>
+        <v>0.02518450355600482</v>
       </c>
       <c r="W85">
-        <v>0.2297899457971747</v>
+        <v>0.2298614940614941</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1592995706855728</v>
+        <v>0.1574031472250302</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.258710536520924</v>
+        <v>0.260610536520924</v>
       </c>
       <c r="C86">
-        <v>-188.2498128670611</v>
+        <v>-192.5373740445022</v>
       </c>
       <c r="D86">
-        <v>96.72818713293881</v>
+        <v>95.87262595549775</v>
       </c>
       <c r="E86">
-        <v>233.4879999999999</v>
+        <v>236.92</v>
       </c>
       <c r="F86">
-        <v>288.288</v>
+        <v>291.72</v>
       </c>
       <c r="G86">
         <v>3.31</v>
@@ -8333,37 +8333,37 @@
         <v>10.7</v>
       </c>
       <c r="M86">
-        <v>67.9783104</v>
+        <v>68.787576</v>
       </c>
       <c r="N86">
-        <v>-57.2783104</v>
+        <v>-58.087576</v>
       </c>
       <c r="O86">
-        <v>-9.164529664</v>
+        <v>-9.294012159999999</v>
       </c>
       <c r="P86">
-        <v>-48.113780736</v>
+        <v>-48.79356384</v>
       </c>
       <c r="Q86">
-        <v>-35.91378073599999</v>
+        <v>-36.59356384</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4101680094329309</v>
+        <v>0.434459210061793</v>
       </c>
       <c r="T86">
-        <v>5.01566279977862</v>
+        <v>5.350040319763862</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02518450355600483</v>
+        <v>0.02488821527887536</v>
       </c>
       <c r="W86">
-        <v>0.2298614940614941</v>
+        <v>0.2299313588372412</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1574031472250302</v>
+        <v>0.155551345492971</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.260610536520924</v>
+        <v>0.262510536520924</v>
       </c>
       <c r="C87">
-        <v>-192.5373740445022</v>
+        <v>-196.8099330327259</v>
       </c>
       <c r="D87">
-        <v>95.87262595549775</v>
+        <v>95.03206696727406</v>
       </c>
       <c r="E87">
-        <v>236.92</v>
+        <v>240.352</v>
       </c>
       <c r="F87">
-        <v>291.72</v>
+        <v>295.152</v>
       </c>
       <c r="G87">
         <v>3.31</v>
@@ -8415,37 +8415,37 @@
         <v>10.7</v>
       </c>
       <c r="M87">
-        <v>68.787576</v>
+        <v>69.5968416</v>
       </c>
       <c r="N87">
-        <v>-58.087576</v>
+        <v>-58.8968416</v>
       </c>
       <c r="O87">
-        <v>-9.294012159999999</v>
+        <v>-9.423494656000001</v>
       </c>
       <c r="P87">
-        <v>-48.79356384</v>
+        <v>-49.473346944</v>
       </c>
       <c r="Q87">
-        <v>-36.59356384</v>
+        <v>-37.273346944</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.434459210061793</v>
+        <v>0.462220582209064</v>
       </c>
       <c r="T87">
-        <v>5.350040319763862</v>
+        <v>5.732186056889852</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02488821527887536</v>
+        <v>0.02459881742679541</v>
       </c>
       <c r="W87">
-        <v>0.2299313588372412</v>
+        <v>0.2299995988507617</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.155551345492971</v>
+        <v>0.1537426089174714</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.262510536520924</v>
+        <v>0.264410536520924</v>
       </c>
       <c r="C88">
-        <v>-196.8099330327259</v>
+        <v>-201.0678809953052</v>
       </c>
       <c r="D88">
-        <v>95.03206696727406</v>
+        <v>94.20611900469474</v>
       </c>
       <c r="E88">
-        <v>240.352</v>
+        <v>243.784</v>
       </c>
       <c r="F88">
-        <v>295.152</v>
+        <v>298.584</v>
       </c>
       <c r="G88">
         <v>3.31</v>
@@ -8497,37 +8497,37 @@
         <v>10.7</v>
       </c>
       <c r="M88">
-        <v>69.5968416</v>
+        <v>70.40610720000001</v>
       </c>
       <c r="N88">
-        <v>-58.8968416</v>
+        <v>-59.70610720000001</v>
       </c>
       <c r="O88">
-        <v>-9.423494656000001</v>
+        <v>-9.552977152</v>
       </c>
       <c r="P88">
-        <v>-49.473346944</v>
+        <v>-50.15313004800001</v>
       </c>
       <c r="Q88">
-        <v>-37.273346944</v>
+        <v>-37.95313004800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.462220582209064</v>
+        <v>0.4942529346866843</v>
       </c>
       <c r="T88">
-        <v>5.732186056889852</v>
+        <v>6.173123445881379</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02459881742679541</v>
+        <v>0.02431607239890121</v>
       </c>
       <c r="W88">
-        <v>0.2299995988507617</v>
+        <v>0.2300662701283391</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1537426089174714</v>
+        <v>0.1519754524931326</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.264410536520924</v>
+        <v>0.266310536520924</v>
       </c>
       <c r="C89">
-        <v>-201.0678809953052</v>
+        <v>-205.3115956141753</v>
       </c>
       <c r="D89">
-        <v>94.20611900469474</v>
+        <v>93.39440438582469</v>
       </c>
       <c r="E89">
-        <v>243.784</v>
+        <v>247.216</v>
       </c>
       <c r="F89">
-        <v>298.584</v>
+        <v>302.016</v>
       </c>
       <c r="G89">
         <v>3.31</v>
@@ -8579,37 +8579,37 @@
         <v>10.7</v>
       </c>
       <c r="M89">
-        <v>70.40610720000001</v>
+        <v>71.21537280000001</v>
       </c>
       <c r="N89">
-        <v>-59.70610720000001</v>
+        <v>-60.51537280000001</v>
       </c>
       <c r="O89">
-        <v>-9.552977152</v>
+        <v>-9.682459648000002</v>
       </c>
       <c r="P89">
-        <v>-50.15313004800001</v>
+        <v>-50.832913152</v>
       </c>
       <c r="Q89">
-        <v>-37.95313004800001</v>
+        <v>-38.632913152</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4942529346866843</v>
+        <v>0.5316240125772412</v>
       </c>
       <c r="T89">
-        <v>6.173123445881379</v>
+        <v>6.687550399704827</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02431607239890121</v>
+        <v>0.02403975339436824</v>
       </c>
       <c r="W89">
-        <v>0.2300662701283391</v>
+        <v>0.230131426149608</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1519754524931326</v>
+        <v>0.1502484587148015</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.266310536520924</v>
+        <v>0.268210536520924</v>
       </c>
       <c r="C90">
-        <v>-205.3115956141753</v>
+        <v>-209.5414416654858</v>
       </c>
       <c r="D90">
-        <v>93.39440438582469</v>
+        <v>92.59655833451419</v>
       </c>
       <c r="E90">
-        <v>247.216</v>
+        <v>250.648</v>
       </c>
       <c r="F90">
-        <v>302.016</v>
+        <v>305.448</v>
       </c>
       <c r="G90">
         <v>3.31</v>
@@ -8661,37 +8661,37 @@
         <v>10.7</v>
       </c>
       <c r="M90">
-        <v>71.21537280000001</v>
+        <v>72.0246384</v>
       </c>
       <c r="N90">
-        <v>-60.51537280000001</v>
+        <v>-61.3246384</v>
       </c>
       <c r="O90">
-        <v>-9.682459648000002</v>
+        <v>-9.811942144</v>
       </c>
       <c r="P90">
-        <v>-50.832913152</v>
+        <v>-51.512696256</v>
       </c>
       <c r="Q90">
-        <v>-38.632913152</v>
+        <v>-39.312696256</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5316240125772412</v>
+        <v>0.5757898319024451</v>
       </c>
       <c r="T90">
-        <v>6.687550399704827</v>
+        <v>7.295509526950723</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02403975339436824</v>
+        <v>0.02376964380566748</v>
       </c>
       <c r="W90">
-        <v>0.230131426149608</v>
+        <v>0.2301951179906236</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1502484587148015</v>
+        <v>0.1485602737854218</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.268210536520924</v>
+        <v>0.270110536520924</v>
       </c>
       <c r="C91">
-        <v>-209.5414416654858</v>
+        <v>-213.7577715661865</v>
       </c>
       <c r="D91">
-        <v>92.59655833451419</v>
+        <v>91.81222843381349</v>
       </c>
       <c r="E91">
-        <v>250.648</v>
+        <v>254.08</v>
       </c>
       <c r="F91">
-        <v>305.448</v>
+        <v>308.88</v>
       </c>
       <c r="G91">
         <v>3.31</v>
@@ -8743,37 +8743,37 @@
         <v>10.7</v>
       </c>
       <c r="M91">
-        <v>72.0246384</v>
+        <v>72.833904</v>
       </c>
       <c r="N91">
-        <v>-61.3246384</v>
+        <v>-62.133904</v>
       </c>
       <c r="O91">
-        <v>-9.811942144</v>
+        <v>-9.941424640000001</v>
       </c>
       <c r="P91">
-        <v>-51.512696256</v>
+        <v>-52.19247936</v>
       </c>
       <c r="Q91">
-        <v>-39.312696256</v>
+        <v>-39.99247936</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5757898319024451</v>
+        <v>0.6287888150926897</v>
       </c>
       <c r="T91">
-        <v>7.295509526950723</v>
+        <v>8.025060479645795</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02376964380566748</v>
+        <v>0.02350553665227117</v>
       </c>
       <c r="W91">
-        <v>0.2301951179906236</v>
+        <v>0.2302573944573945</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1485602737854218</v>
+        <v>0.1469096040766948</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.270110536520924</v>
+        <v>0.272010536520924</v>
       </c>
       <c r="C92">
-        <v>-213.7577715661865</v>
+        <v>-217.9609258930678</v>
       </c>
       <c r="D92">
-        <v>91.81222843381349</v>
+        <v>91.0410741069322</v>
       </c>
       <c r="E92">
-        <v>254.08</v>
+        <v>257.512</v>
       </c>
       <c r="F92">
-        <v>308.88</v>
+        <v>312.312</v>
       </c>
       <c r="G92">
         <v>3.31</v>
@@ -8825,37 +8825,37 @@
         <v>10.7</v>
       </c>
       <c r="M92">
-        <v>72.833904</v>
+        <v>73.64316960000001</v>
       </c>
       <c r="N92">
-        <v>-62.133904</v>
+        <v>-62.9431696</v>
       </c>
       <c r="O92">
-        <v>-9.941424640000001</v>
+        <v>-10.070907136</v>
       </c>
       <c r="P92">
-        <v>-52.19247936</v>
+        <v>-52.872262464</v>
       </c>
       <c r="Q92">
-        <v>-39.99247936</v>
+        <v>-40.672262464</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6287888150926897</v>
+        <v>0.6935653501029886</v>
       </c>
       <c r="T92">
-        <v>8.025060479645795</v>
+        <v>8.916733866273107</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02350553665227117</v>
+        <v>0.02324723405169676</v>
       </c>
       <c r="W92">
-        <v>0.2302573944573945</v>
+        <v>0.2303183022106099</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1469096040766948</v>
+        <v>0.1452952128231048</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.272010536520924</v>
+        <v>0.273910536520924</v>
       </c>
       <c r="C93">
-        <v>-217.9609258930678</v>
+        <v>-222.1512338758615</v>
       </c>
       <c r="D93">
-        <v>91.0410741069322</v>
+        <v>90.2827661241385</v>
       </c>
       <c r="E93">
-        <v>257.512</v>
+        <v>260.944</v>
       </c>
       <c r="F93">
-        <v>312.312</v>
+        <v>315.744</v>
       </c>
       <c r="G93">
         <v>3.31</v>
@@ -8907,37 +8907,37 @@
         <v>10.7</v>
       </c>
       <c r="M93">
-        <v>73.64316960000001</v>
+        <v>74.45243520000001</v>
       </c>
       <c r="N93">
-        <v>-62.9431696</v>
+        <v>-63.75243520000001</v>
       </c>
       <c r="O93">
-        <v>-10.070907136</v>
+        <v>-10.200389632</v>
       </c>
       <c r="P93">
-        <v>-52.872262464</v>
+        <v>-53.552045568</v>
       </c>
       <c r="Q93">
-        <v>-40.672262464</v>
+        <v>-41.35204556800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6935653501029886</v>
+        <v>0.7745360188658623</v>
       </c>
       <c r="T93">
-        <v>8.916733866273107</v>
+        <v>10.03132559955725</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02324723405169676</v>
+        <v>0.02299454672504788</v>
       </c>
       <c r="W93">
-        <v>0.2303183022106099</v>
+        <v>0.2303778858822337</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1452952128231048</v>
+        <v>0.1437159170315493</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.273910536520924</v>
+        <v>0.275810536520924</v>
       </c>
       <c r="C94">
-        <v>-222.1512338758615</v>
+        <v>-226.3290138659023</v>
       </c>
       <c r="D94">
-        <v>90.2827661241385</v>
+        <v>89.53698613409765</v>
       </c>
       <c r="E94">
-        <v>260.944</v>
+        <v>264.376</v>
       </c>
       <c r="F94">
-        <v>315.744</v>
+        <v>319.176</v>
       </c>
       <c r="G94">
         <v>3.31</v>
@@ -8989,37 +8989,37 @@
         <v>10.7</v>
       </c>
       <c r="M94">
-        <v>74.45243520000001</v>
+        <v>75.2617008</v>
       </c>
       <c r="N94">
-        <v>-63.75243520000001</v>
+        <v>-64.5617008</v>
       </c>
       <c r="O94">
-        <v>-10.200389632</v>
+        <v>-10.329872128</v>
       </c>
       <c r="P94">
-        <v>-53.552045568</v>
+        <v>-54.231828672</v>
       </c>
       <c r="Q94">
-        <v>-41.35204556800001</v>
+        <v>-42.031828672</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7745360188658623</v>
+        <v>0.8786411644181286</v>
       </c>
       <c r="T94">
-        <v>10.03132559955725</v>
+        <v>11.46437211377971</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02299454672504788</v>
+        <v>0.02274729353445597</v>
       </c>
       <c r="W94">
-        <v>0.2303778858822337</v>
+        <v>0.2304361881845753</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1437159170315493</v>
+        <v>0.1421705845903499</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.275810536520924</v>
+        <v>0.277710536520924</v>
       </c>
       <c r="C95">
-        <v>-226.3290138659023</v>
+        <v>-230.4945737817513</v>
       </c>
       <c r="D95">
-        <v>89.53698613409765</v>
+        <v>88.80342621824867</v>
       </c>
       <c r="E95">
-        <v>264.376</v>
+        <v>267.808</v>
       </c>
       <c r="F95">
-        <v>319.176</v>
+        <v>322.608</v>
       </c>
       <c r="G95">
         <v>3.31</v>
@@ -9071,37 +9071,37 @@
         <v>10.7</v>
       </c>
       <c r="M95">
-        <v>75.2617008</v>
+        <v>76.0709664</v>
       </c>
       <c r="N95">
-        <v>-64.5617008</v>
+        <v>-65.3709664</v>
       </c>
       <c r="O95">
-        <v>-10.329872128</v>
+        <v>-10.459354624</v>
       </c>
       <c r="P95">
-        <v>-54.231828672</v>
+        <v>-54.911611776</v>
       </c>
       <c r="Q95">
-        <v>-42.031828672</v>
+        <v>-42.711611776</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8786411644181286</v>
+        <v>1.017448025154484</v>
       </c>
       <c r="T95">
-        <v>11.46437211377971</v>
+        <v>13.37510079940967</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02274729353445597</v>
+        <v>0.02250530105004687</v>
       </c>
       <c r="W95">
-        <v>0.2304361881845753</v>
+        <v>0.230493250012399</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1421705845903499</v>
+        <v>0.1406581315627929</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.277710536520924</v>
+        <v>0.279610536520924</v>
       </c>
       <c r="C96">
-        <v>-230.4945737817513</v>
+        <v>-234.6482115330919</v>
       </c>
       <c r="D96">
-        <v>88.80342621824867</v>
+        <v>88.08178846690816</v>
       </c>
       <c r="E96">
-        <v>267.808</v>
+        <v>271.24</v>
       </c>
       <c r="F96">
-        <v>322.608</v>
+        <v>326.04</v>
       </c>
       <c r="G96">
         <v>3.31</v>
@@ -9153,37 +9153,37 @@
         <v>10.7</v>
       </c>
       <c r="M96">
-        <v>76.0709664</v>
+        <v>76.88023200000001</v>
       </c>
       <c r="N96">
-        <v>-65.3709664</v>
+        <v>-66.180232</v>
       </c>
       <c r="O96">
-        <v>-10.459354624</v>
+        <v>-10.58883712</v>
       </c>
       <c r="P96">
-        <v>-54.911611776</v>
+        <v>-55.59139488</v>
       </c>
       <c r="Q96">
-        <v>-42.711611776</v>
+        <v>-43.39139488000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.017448025154484</v>
+        <v>1.211777630185381</v>
       </c>
       <c r="T96">
-        <v>13.37510079940967</v>
+        <v>16.05012095929161</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02250530105004687</v>
+        <v>0.0222684031442569</v>
       </c>
       <c r="W96">
-        <v>0.230493250012399</v>
+        <v>0.2305491105385842</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1406581315627929</v>
+        <v>0.1391775196516056</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.279610536520924</v>
+        <v>0.2815105365209239</v>
       </c>
       <c r="C97">
-        <v>-234.6482115330919</v>
+        <v>-238.790215424124</v>
       </c>
       <c r="D97">
-        <v>88.08178846690816</v>
+        <v>87.37178457587608</v>
       </c>
       <c r="E97">
-        <v>271.24</v>
+        <v>274.672</v>
       </c>
       <c r="F97">
-        <v>326.04</v>
+        <v>329.472</v>
       </c>
       <c r="G97">
         <v>3.31</v>
@@ -9235,37 +9235,37 @@
         <v>10.7</v>
       </c>
       <c r="M97">
-        <v>76.88023200000001</v>
+        <v>77.68949760000001</v>
       </c>
       <c r="N97">
-        <v>-66.180232</v>
+        <v>-66.98949760000001</v>
       </c>
       <c r="O97">
-        <v>-10.58883712</v>
+        <v>-10.718319616</v>
       </c>
       <c r="P97">
-        <v>-55.59139488</v>
+        <v>-56.271177984</v>
       </c>
       <c r="Q97">
-        <v>-43.39139488000001</v>
+        <v>-44.071177984</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.211777630185381</v>
+        <v>1.503272037731727</v>
       </c>
       <c r="T97">
-        <v>16.05012095929161</v>
+        <v>20.06265119911452</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0222684031442569</v>
+        <v>0.02203644061150422</v>
       </c>
       <c r="W97">
-        <v>0.2305491105385842</v>
+        <v>0.2306038073038073</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1391775196516056</v>
+        <v>0.1377277538219014</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.281510536520924</v>
+        <v>0.283410536520924</v>
       </c>
       <c r="C98">
-        <v>-238.7902154241239</v>
+        <v>-242.9208645376053</v>
       </c>
       <c r="D98">
-        <v>87.37178457587603</v>
+        <v>86.67313546239473</v>
       </c>
       <c r="E98">
-        <v>274.672</v>
+        <v>278.104</v>
       </c>
       <c r="F98">
-        <v>329.472</v>
+        <v>332.904</v>
       </c>
       <c r="G98">
         <v>3.31</v>
@@ -9317,37 +9317,37 @@
         <v>10.7</v>
       </c>
       <c r="M98">
-        <v>77.6894976</v>
+        <v>78.4987632</v>
       </c>
       <c r="N98">
-        <v>-66.98949759999999</v>
+        <v>-67.7987632</v>
       </c>
       <c r="O98">
-        <v>-10.718319616</v>
+        <v>-10.847802112</v>
       </c>
       <c r="P98">
-        <v>-56.27117798399999</v>
+        <v>-56.950961088</v>
       </c>
       <c r="Q98">
-        <v>-44.07117798399999</v>
+        <v>-44.750961088</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.503272037731723</v>
+        <v>1.989096050308964</v>
       </c>
       <c r="T98">
-        <v>20.06265119911447</v>
+        <v>26.75020159881929</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02203644061150423</v>
+        <v>0.02180926081138563</v>
       </c>
       <c r="W98">
-        <v>0.2306038073038073</v>
+        <v>0.2306573763006753</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1377277538219015</v>
+        <v>0.1363078800711602</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.283410536520924</v>
+        <v>0.285310536520924</v>
       </c>
       <c r="C99">
-        <v>-242.9208645376053</v>
+        <v>-247.0404291006121</v>
       </c>
       <c r="D99">
-        <v>86.67313546239473</v>
+        <v>85.98557089938787</v>
       </c>
       <c r="E99">
-        <v>278.104</v>
+        <v>281.5359999999999</v>
       </c>
       <c r="F99">
-        <v>332.904</v>
+        <v>336.336</v>
       </c>
       <c r="G99">
         <v>3.31</v>
@@ -9399,37 +9399,37 @@
         <v>10.7</v>
       </c>
       <c r="M99">
-        <v>78.4987632</v>
+        <v>79.30802879999999</v>
       </c>
       <c r="N99">
-        <v>-67.7987632</v>
+        <v>-68.60802879999999</v>
       </c>
       <c r="O99">
-        <v>-10.847802112</v>
+        <v>-10.977284608</v>
       </c>
       <c r="P99">
-        <v>-56.950961088</v>
+        <v>-57.63074419199999</v>
       </c>
       <c r="Q99">
-        <v>-44.750961088</v>
+        <v>-45.43074419199999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.989096050308964</v>
+        <v>2.960744075463445</v>
       </c>
       <c r="T99">
-        <v>26.75020159881929</v>
+        <v>40.12530239822893</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02180926081138563</v>
+        <v>0.02158671733371843</v>
       </c>
       <c r="W99">
-        <v>0.2306573763006753</v>
+        <v>0.2307098520527092</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1363078800711602</v>
+        <v>0.1349169833357402</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.285310536520924</v>
+        <v>0.287210536520924</v>
       </c>
       <c r="C100">
-        <v>-247.0404291006121</v>
+        <v>-251.1491708330289</v>
       </c>
       <c r="D100">
-        <v>85.98557089938787</v>
+        <v>85.30882916697108</v>
       </c>
       <c r="E100">
-        <v>281.5359999999999</v>
+        <v>284.968</v>
       </c>
       <c r="F100">
-        <v>336.336</v>
+        <v>339.768</v>
       </c>
       <c r="G100">
         <v>3.31</v>
@@ -9481,37 +9481,37 @@
         <v>10.7</v>
       </c>
       <c r="M100">
-        <v>79.30802879999999</v>
+        <v>80.11729439999999</v>
       </c>
       <c r="N100">
-        <v>-68.60802879999999</v>
+        <v>-69.41729439999999</v>
       </c>
       <c r="O100">
-        <v>-10.977284608</v>
+        <v>-11.106767104</v>
       </c>
       <c r="P100">
-        <v>-57.63074419199999</v>
+        <v>-58.31052729599999</v>
       </c>
       <c r="Q100">
-        <v>-45.43074419199999</v>
+        <v>-46.11052729599999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.960744075463445</v>
+        <v>5.875688150926892</v>
       </c>
       <c r="T100">
-        <v>40.12530239822893</v>
+        <v>80.25060479645788</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02158671733371843</v>
+        <v>0.02136866968388289</v>
       </c>
       <c r="W100">
-        <v>0.2307098520527092</v>
+        <v>0.2307612676885404</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1349169833357402</v>
+        <v>0.1335541855242681</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.287210536520924</v>
-      </c>
-      <c r="C101">
-        <v>-251.1491708330289</v>
-      </c>
-      <c r="D101">
-        <v>85.30882916697108</v>
-      </c>
-      <c r="E101">
-        <v>284.968</v>
-      </c>
-      <c r="F101">
-        <v>339.768</v>
-      </c>
-      <c r="G101">
-        <v>3.31</v>
-      </c>
-      <c r="H101">
-        <v>288.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.9</v>
-      </c>
-      <c r="K101">
-        <v>12.2</v>
-      </c>
-      <c r="L101">
-        <v>10.7</v>
-      </c>
-      <c r="M101">
-        <v>80.11729439999999</v>
-      </c>
-      <c r="N101">
-        <v>-69.41729439999999</v>
-      </c>
-      <c r="O101">
-        <v>-11.106767104</v>
-      </c>
-      <c r="P101">
-        <v>-58.31052729599999</v>
-      </c>
-      <c r="Q101">
-        <v>-46.11052729599999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.875688150926892</v>
-      </c>
-      <c r="T101">
-        <v>80.25060479645788</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02136866968388289</v>
-      </c>
-      <c r="W101">
-        <v>0.2307612676885404</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1335541855242681</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
